--- a/KAMCHATKA_REESTR_MPT.xlsx
+++ b/KAMCHATKA_REESTR_MPT.xlsx
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>147</v>
+        <v>20</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L2" s="6" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L3" s="6" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>ООО «Челябинский завод трубопроводной арматуры» +7 (351) 215-53-33 zakaz@chzta.ru</t>
+          <t>ООО «Челябинский завод трубопроводной арматуры» +7 (351) 215-53-33 zakaz@chzta.ru | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr"/>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -1418,20 +1418,32 @@
       <c r="E15" s="6" t="inlineStr"/>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="8" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые латунные LD DN15-50 PN до 4,0 — изготовитель ЛД Прайд, не ЧСГС; источник https://torgs.ru/industrial-products/542786/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr"/>
@@ -1456,20 +1468,32 @@
       <c r="E16" s="6" t="inlineStr"/>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr"/>
-      <c r="H16" s="8" t="inlineStr"/>
-      <c r="I16" s="6" t="inlineStr"/>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые латунные LD DN15-50 PN до 4,0 — изготовитель ЛД Прайд, не ЧСГС; источник https://torgs.ru/industrial-products/542786/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr"/>
@@ -1494,20 +1518,32 @@
       <c r="E17" s="6" t="inlineStr"/>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="inlineStr"/>
-      <c r="H17" s="8" t="inlineStr"/>
-      <c r="I17" s="6" t="inlineStr"/>
-      <c r="J17" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые латунные LD DN15-50 PN до 4,0 — изготовитель ЛД Прайд, не ЧСГС; источник https://torgs.ru/industrial-products/542786/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr"/>
@@ -1532,20 +1568,32 @@
       <c r="E18" s="6" t="inlineStr"/>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr"/>
-      <c r="H18" s="8" t="inlineStr"/>
-      <c r="I18" s="6" t="inlineStr"/>
-      <c r="J18" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые латунные LD DN15-50 PN до 4,0 — изготовитель ЛД Прайд, не ЧСГС; источник https://torgs.ru/industrial-products/542786/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr"/>
@@ -1570,20 +1618,32 @@
       <c r="E19" s="6" t="inlineStr"/>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="8" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые латунные LD DN15-50 PN до 4,0 — изготовитель ЛД Прайд, не ЧСГС; источник https://torgs.ru/industrial-products/542786/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr"/>
@@ -1608,20 +1668,32 @@
       <c r="E20" s="6" t="inlineStr"/>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="8" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые латунные LD DN15-50 PN до 4,0 — изготовитель ЛД Прайд, не ЧСГС; источник https://torgs.ru/industrial-products/542786/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr"/>
@@ -1646,20 +1718,32 @@
       <c r="E21" s="6" t="inlineStr"/>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="8" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr"/>
@@ -1684,20 +1768,32 @@
       <c r="E22" s="6" t="inlineStr"/>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr"/>
-      <c r="H22" s="8" t="inlineStr"/>
-      <c r="I22" s="6" t="inlineStr"/>
-      <c r="J22" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr"/>
@@ -1722,20 +1818,32 @@
       <c r="E23" s="6" t="inlineStr"/>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr"/>
-      <c r="H23" s="8" t="inlineStr"/>
-      <c r="I23" s="6" t="inlineStr"/>
-      <c r="J23" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ПромАрм»</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>10655456</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>24.07.2028</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>ООО «ПромАрм» +7 (8412) 35-07-97 info@promarm.ru; АО «Пензтяжпромарматура» 8 800 444-00-28 (продажи) sales@ptpa.ru; АО «Пензенский арматурный завод» +7 (8412) 20-11-00 info@armpaz.ru</t>
+          <t>Затворы поворотные дисковые ПА; источник https://torgs.ru/industrial-products/387291/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr"/>
@@ -1760,20 +1868,32 @@
       <c r="E24" s="6" t="inlineStr"/>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr"/>
-      <c r="H24" s="8" t="inlineStr"/>
-      <c r="I24" s="6" t="inlineStr"/>
-      <c r="J24" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ПромАрм»</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>10655456</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>24.07.2028</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>ООО «ПромАрм» +7 (8412) 35-07-97 info@promarm.ru; АО «Пензтяжпромарматура» 8 800 444-00-28 (продажи) sales@ptpa.ru; АО «Пензенский арматурный завод» +7 (8412) 20-11-00 info@armpaz.ru</t>
+          <t>Затворы поворотные дисковые ПА; источник https://torgs.ru/industrial-products/387291/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr"/>
@@ -1802,7 +1922,7 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>АО «Тулаэлектропривод»</t>
+          <t>АО «ПО «Тулаэлектропривод» (ИНН 7130025182)</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -1810,16 +1930,24 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>Российский производитель — запросить номер</t>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>10612591</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>12.02.2028</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>Тулаэлектропривод</t>
+          <t>Электроприводы многооборотные — сверить ТУ Н-В-02 с паспортом; источник https://torgs.ru/industrial-products/345520/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
@@ -1848,20 +1976,32 @@
       <c r="E26" s="6" t="inlineStr"/>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="8" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr"/>
@@ -1886,20 +2026,32 @@
       <c r="E27" s="6" t="inlineStr"/>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="8" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr"/>
@@ -1924,20 +2076,32 @@
       <c r="E28" s="6" t="inlineStr"/>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr"/>
-      <c r="H28" s="8" t="inlineStr"/>
-      <c r="I28" s="6" t="inlineStr"/>
-      <c r="J28" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr"/>
@@ -1962,20 +2126,32 @@
       <c r="E29" s="6" t="inlineStr"/>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr"/>
-      <c r="H29" s="8" t="inlineStr"/>
-      <c r="I29" s="6" t="inlineStr"/>
-      <c r="J29" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr"/>
@@ -2000,20 +2176,32 @@
       <c r="E30" s="6" t="inlineStr"/>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr"/>
-      <c r="H30" s="8" t="inlineStr"/>
-      <c r="I30" s="6" t="inlineStr"/>
-      <c r="J30" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr"/>
@@ -2059,7 +2247,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
@@ -2101,7 +2289,7 @@
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>ООО «Арма-Пром» +7 (4725) 469-470 (завод) zavod@saz-avangard.ru</t>
+          <t>ООО «Арма-Пром» +7 (4725) 469-470 (завод) zavod@saz-avangard.ru | Арма-Пром: записи 10232737/10232729/10232727 истекли 28.08.2026 (по зеркалу) — запросить новую запись у завода</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr"/>
@@ -2139,7 +2327,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>ООО «Арма-Пром» +7 (4725) 469-470 (завод) zavod@saz-avangard.ru</t>
+          <t>ООО «Арма-Пром» +7 (4725) 469-470 (завод) zavod@saz-avangard.ru | Арма-Пром: записи 10232737/10232729/10232727 истекли 28.08.2026 (по зеркалу) — запросить новую запись у завода</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
@@ -2177,7 +2365,7 @@
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>ООО «Арма-Пром» +7 (4725) 469-470 (завод) zavod@saz-avangard.ru</t>
+          <t>ООО «Арма-Пром» +7 (4725) 469-470 (завод) zavod@saz-avangard.ru | Арма-Пром: записи 10232737/10232729/10232727 истекли 28.08.2026 (по зеркалу) — запросить новую запись у завода</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr"/>
@@ -2215,7 +2403,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>ООО «Арма-Пром» +7 (4725) 469-470 (завод) zavod@saz-avangard.ru</t>
+          <t>ООО «Арма-Пром» +7 (4725) 469-470 (завод) zavod@saz-avangard.ru | Арма-Пром: записи 10232737/10232729/10232727 истекли 28.08.2026 (по зеркалу) — запросить новую запись у завода</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
@@ -2261,7 +2449,7 @@
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr">
@@ -2311,7 +2499,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr">
@@ -2361,7 +2549,7 @@
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
@@ -2411,7 +2599,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
@@ -2461,7 +2649,7 @@
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr">
@@ -2511,7 +2699,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
@@ -2561,7 +2749,7 @@
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
@@ -2611,7 +2799,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
@@ -2661,7 +2849,7 @@
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr">
@@ -2711,7 +2899,7 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr">
@@ -2761,7 +2949,7 @@
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr">
@@ -2811,7 +2999,7 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr">
@@ -2861,7 +3049,7 @@
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr">
@@ -2911,7 +3099,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr">
@@ -2961,7 +3149,7 @@
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr">
@@ -3011,7 +3199,7 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr">
@@ -3061,7 +3249,7 @@
       </c>
       <c r="K52" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L52" s="6" t="inlineStr">
@@ -3090,20 +3278,32 @@
       <c r="E53" s="6" t="inlineStr"/>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr"/>
-      <c r="H53" s="8" t="inlineStr"/>
-      <c r="I53" s="6" t="inlineStr"/>
-      <c r="J53" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ПТЗ» (Пермь)</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>10746921</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>23.11.2028</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>ООО «Пермский трубопроводный завод» +7 (342) 270-07-34 sales@ptza.ru; ООО «Челябинский завод трубопроводной арматуры» +7 (351) 215-53-33 zakaz@chzta.ru</t>
+          <t>Клапан обратный подъёмный; источник https://torgs.ru/industrial-products/502692/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr"/>
@@ -3128,20 +3328,32 @@
       <c r="E54" s="6" t="inlineStr"/>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr"/>
-      <c r="H54" s="8" t="inlineStr"/>
-      <c r="I54" s="6" t="inlineStr"/>
-      <c r="J54" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ПТЗ» (Пермь)</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>10746921</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>23.11.2028</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
-          <t>ООО «Пермский трубопроводный завод» +7 (342) 270-07-34 sales@ptza.ru; ООО «Челябинский завод трубопроводной арматуры» +7 (351) 215-53-33 zakaz@chzta.ru</t>
+          <t>Клапан обратный подъёмный; источник https://torgs.ru/industrial-products/502692/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L54" s="6" t="inlineStr"/>
@@ -3187,7 +3399,7 @@
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L55" s="6" t="inlineStr">
@@ -3237,7 +3449,7 @@
       </c>
       <c r="K56" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L56" s="6" t="inlineStr">
@@ -3287,7 +3499,7 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L57" s="6" t="inlineStr">
@@ -3337,7 +3549,7 @@
       </c>
       <c r="K58" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr">
@@ -3387,7 +3599,7 @@
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L59" s="6" t="inlineStr">
@@ -3437,7 +3649,7 @@
       </c>
       <c r="K60" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L60" s="6" t="inlineStr">
@@ -3487,7 +3699,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr">
@@ -3529,7 +3741,7 @@
       </c>
       <c r="K62" s="6" t="inlineStr">
         <is>
-          <t>поставщик не найден</t>
+          <t>поставщик не найден | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr"/>
@@ -3567,7 +3779,7 @@
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>поставщик не найден</t>
+          <t>поставщик не найден | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L63" s="6" t="inlineStr"/>
@@ -3605,7 +3817,7 @@
       </c>
       <c r="K64" s="6" t="inlineStr">
         <is>
-          <t>поставщик не найден</t>
+          <t>поставщик не найден | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L64" s="6" t="inlineStr"/>
@@ -3651,7 +3863,7 @@
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr">
@@ -3701,7 +3913,7 @@
       </c>
       <c r="K66" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L66" s="6" t="inlineStr">
@@ -3751,7 +3963,7 @@
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr">
@@ -3801,7 +4013,7 @@
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr">
@@ -3851,7 +4063,7 @@
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>КИПИКА (прайс 01.10)</t>
+          <t>КИПИКА (прайс 01.10) | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
@@ -3893,7 +4105,7 @@
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>Компания «Арматон» +7 (963) 728-59-82 armaton@bk.ru</t>
+          <t>Компания «Арматон» +7 (963) 728-59-82 armaton@bk.ru | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr"/>
@@ -3939,7 +4151,7 @@
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr">
@@ -3989,7 +4201,7 @@
       </c>
       <c r="K72" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L72" s="6" t="inlineStr">
@@ -4039,7 +4251,7 @@
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr">
@@ -4089,7 +4301,7 @@
       </c>
       <c r="K74" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr">
@@ -4131,7 +4343,7 @@
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>Компания «Арматон» +7 (963) 728-59-82 armaton@bk.ru; ООО «Нижегородский завод «Старт» +7 (831) 253-83-11 start.nn@mail.ru</t>
+          <t>Компания «Арматон» +7 (963) 728-59-82 armaton@bk.ru; ООО «Нижегородский завод «Старт» +7 (831) 253-83-11 start.nn@mail.ru | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
@@ -4169,7 +4381,7 @@
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>Компания «Арматон» +7 (963) 728-59-82 armaton@bk.ru; ООО «Нижегородский завод «Старт» +7 (831) 253-83-11 start.nn@mail.ru</t>
+          <t>Компания «Арматон» +7 (963) 728-59-82 armaton@bk.ru; ООО «Нижегородский завод «Старт» +7 (831) 253-83-11 start.nn@mail.ru | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr"/>
@@ -4207,7 +4419,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>Компания «Арматон» +7 (963) 728-59-82 armaton@bk.ru; ООО «Нижегородский завод «Старт» +7 (831) 253-83-11 start.nn@mail.ru</t>
+          <t>Компания «Арматон» +7 (963) 728-59-82 armaton@bk.ru; ООО «Нижегородский завод «Старт» +7 (831) 253-83-11 start.nn@mail.ru | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr"/>
@@ -4253,7 +4465,7 @@
       </c>
       <c r="K78" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L78" s="6" t="inlineStr">
@@ -4303,7 +4515,7 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr">
@@ -4353,7 +4565,7 @@
       </c>
       <c r="K80" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L80" s="6" t="inlineStr">
@@ -4403,7 +4615,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr">
@@ -4453,7 +4665,7 @@
       </c>
       <c r="K82" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr">
@@ -4503,7 +4715,7 @@
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr">
@@ -4553,7 +4765,7 @@
       </c>
       <c r="K84" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L84" s="6" t="inlineStr">
@@ -4603,7 +4815,7 @@
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr">
@@ -4632,20 +4844,32 @@
       <c r="E86" s="6" t="inlineStr"/>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr"/>
-      <c r="H86" s="8" t="inlineStr"/>
-      <c r="I86" s="6" t="inlineStr"/>
-      <c r="J86" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ПТЗ» (Пермь)</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>10698937</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>17.02.2031</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K86" s="6" t="inlineStr">
         <is>
-          <t>Компания «Арматон» +7 (963) 728-59-82 armaton@bk.ru; ООО «Пермский трубопроводный завод» +7 (342) 270-07-34 sales@ptza.ru</t>
+          <t>Клапан запорный DN10-600 PN1,6-25; источник https://torgs.ru/industrial-products/502692/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L86" s="6" t="inlineStr"/>
@@ -4670,20 +4894,32 @@
       <c r="E87" s="6" t="inlineStr"/>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr"/>
-      <c r="H87" s="8" t="inlineStr"/>
-      <c r="I87" s="6" t="inlineStr"/>
-      <c r="J87" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ПТЗ» (Пермь)</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>10698937</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>17.02.2031</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>Компания «Арматон» +7 (963) 728-59-82 armaton@bk.ru; ООО «Пермский трубопроводный завод» +7 (342) 270-07-34 sales@ptza.ru</t>
+          <t>Клапан запорный DN10-600 PN1,6-25; источник https://torgs.ru/industrial-products/502692/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr"/>
@@ -4729,7 +4965,7 @@
       </c>
       <c r="K88" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L88" s="6" t="inlineStr">
@@ -4779,7 +5015,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr">
@@ -4829,7 +5065,7 @@
       </c>
       <c r="K90" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L90" s="6" t="inlineStr">
@@ -4879,7 +5115,7 @@
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr">
@@ -4929,7 +5165,7 @@
       </c>
       <c r="K92" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L92" s="6" t="inlineStr">
@@ -4979,7 +5215,7 @@
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr">
@@ -5029,7 +5265,7 @@
       </c>
       <c r="K94" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L94" s="6" t="inlineStr">
@@ -5079,7 +5315,7 @@
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr">
@@ -5129,7 +5365,7 @@
       </c>
       <c r="K96" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L96" s="6" t="inlineStr">
@@ -5179,7 +5415,7 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr">
@@ -5229,7 +5465,7 @@
       </c>
       <c r="K98" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L98" s="6" t="inlineStr">
@@ -5279,7 +5515,7 @@
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr">
@@ -5329,7 +5565,7 @@
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L100" s="6" t="inlineStr">
@@ -5379,7 +5615,7 @@
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr">
@@ -5429,7 +5665,7 @@
       </c>
       <c r="K102" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L102" s="6" t="inlineStr">
@@ -5479,7 +5715,7 @@
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr">
@@ -5529,7 +5765,7 @@
       </c>
       <c r="K104" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L104" s="6" t="inlineStr">
@@ -5579,7 +5815,7 @@
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr">
@@ -5629,7 +5865,7 @@
       </c>
       <c r="K106" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L106" s="6" t="inlineStr">
@@ -5679,7 +5915,7 @@
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr">
@@ -5729,7 +5965,7 @@
       </c>
       <c r="K108" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L108" s="6" t="inlineStr">
@@ -5779,7 +6015,7 @@
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr">
@@ -5829,7 +6065,7 @@
       </c>
       <c r="K110" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L110" s="6" t="inlineStr">
@@ -5879,7 +6115,7 @@
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr">
@@ -5929,7 +6165,7 @@
       </c>
       <c r="K112" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L112" s="6" t="inlineStr">
@@ -5979,7 +6215,7 @@
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr">
@@ -6029,7 +6265,7 @@
       </c>
       <c r="K114" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L114" s="6" t="inlineStr">
@@ -6079,7 +6315,7 @@
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr">
@@ -6129,7 +6365,7 @@
       </c>
       <c r="K116" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L116" s="6" t="inlineStr">
@@ -6179,7 +6415,7 @@
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr">
@@ -6229,7 +6465,7 @@
       </c>
       <c r="K118" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L118" s="6" t="inlineStr">
@@ -6279,7 +6515,7 @@
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr">
@@ -6329,7 +6565,7 @@
       </c>
       <c r="K120" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L120" s="6" t="inlineStr">
@@ -6379,7 +6615,7 @@
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr">
@@ -6429,7 +6665,7 @@
       </c>
       <c r="K122" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L122" s="6" t="inlineStr">
@@ -6479,7 +6715,7 @@
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | если изготовитель ЛМЗ — 10636782 (30ч6бр, до 15.05.2028); у БК-Арматуры уточнить завод</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr">
@@ -6529,7 +6765,7 @@
       </c>
       <c r="K124" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L124" s="6" t="inlineStr">
@@ -6579,7 +6815,7 @@
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | если изготовитель ЛМЗ — 10636782 (30ч6бр, до 15.05.2028); у БК-Арматуры уточнить завод</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr">
@@ -6629,7 +6865,7 @@
       </c>
       <c r="K126" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L126" s="6" t="inlineStr">
@@ -6679,7 +6915,7 @@
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr">
@@ -6729,7 +6965,7 @@
       </c>
       <c r="K128" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L128" s="6" t="inlineStr">
@@ -6779,7 +7015,7 @@
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr">
@@ -6829,7 +7065,7 @@
       </c>
       <c r="K130" s="6" t="inlineStr">
         <is>
-          <t>КИПИКА (прайс 01.10)</t>
+          <t>КИПИКА (прайс 01.10) | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L130" s="6" t="inlineStr">
@@ -6858,20 +7094,32 @@
       <c r="E131" s="6" t="inlineStr"/>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G131" s="6" t="inlineStr"/>
-      <c r="H131" s="8" t="inlineStr"/>
-      <c r="I131" s="6" t="inlineStr"/>
-      <c r="J131" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H131" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые латунные LD DN15-50 PN до 4,0 — изготовитель ЛД Прайд, не ЧСГС; источник https://torgs.ru/industrial-products/542786/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr"/>
@@ -6896,20 +7144,32 @@
       <c r="E132" s="6" t="inlineStr"/>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G132" s="6" t="inlineStr"/>
-      <c r="H132" s="8" t="inlineStr"/>
-      <c r="I132" s="6" t="inlineStr"/>
-      <c r="J132" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H132" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K132" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые латунные LD DN15-50 PN до 4,0 — изготовитель ЛД Прайд, не ЧСГС; источник https://torgs.ru/industrial-products/542786/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L132" s="6" t="inlineStr"/>
@@ -6934,20 +7194,32 @@
       <c r="E133" s="6" t="inlineStr"/>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G133" s="6" t="inlineStr"/>
-      <c r="H133" s="8" t="inlineStr"/>
-      <c r="I133" s="6" t="inlineStr"/>
-      <c r="J133" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H133" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые латунные LD DN15-50 PN до 4,0 — изготовитель ЛД Прайд, не ЧСГС; источник https://torgs.ru/industrial-products/542786/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L133" s="6" t="inlineStr"/>
@@ -6972,20 +7244,32 @@
       <c r="E134" s="6" t="inlineStr"/>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G134" s="6" t="inlineStr"/>
-      <c r="H134" s="8" t="inlineStr"/>
-      <c r="I134" s="6" t="inlineStr"/>
-      <c r="J134" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H134" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K134" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые латунные LD DN15-50 PN до 4,0 — изготовитель ЛД Прайд, не ЧСГС; источник https://torgs.ru/industrial-products/542786/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L134" s="6" t="inlineStr"/>
@@ -7010,20 +7294,32 @@
       <c r="E135" s="6" t="inlineStr"/>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G135" s="6" t="inlineStr"/>
-      <c r="H135" s="8" t="inlineStr"/>
-      <c r="I135" s="6" t="inlineStr"/>
-      <c r="J135" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H135" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
+      <c r="J135" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые латунные LD DN15-50 PN до 4,0 — изготовитель ЛД Прайд, не ЧСГС; источник https://torgs.ru/industrial-products/542786/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L135" s="6" t="inlineStr"/>
@@ -7048,20 +7344,32 @@
       <c r="E136" s="6" t="inlineStr"/>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G136" s="6" t="inlineStr"/>
-      <c r="H136" s="8" t="inlineStr"/>
-      <c r="I136" s="6" t="inlineStr"/>
-      <c r="J136" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H136" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K136" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L136" s="6" t="inlineStr"/>
@@ -7086,20 +7394,32 @@
       <c r="E137" s="6" t="inlineStr"/>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G137" s="6" t="inlineStr"/>
-      <c r="H137" s="8" t="inlineStr"/>
-      <c r="I137" s="6" t="inlineStr"/>
-      <c r="J137" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G137" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H137" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr"/>
@@ -7124,20 +7444,32 @@
       <c r="E138" s="6" t="inlineStr"/>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G138" s="6" t="inlineStr"/>
-      <c r="H138" s="8" t="inlineStr"/>
-      <c r="I138" s="6" t="inlineStr"/>
-      <c r="J138" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H138" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K138" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L138" s="6" t="inlineStr"/>
@@ -7162,20 +7494,32 @@
       <c r="E139" s="6" t="inlineStr"/>
       <c r="F139" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G139" s="6" t="inlineStr"/>
-      <c r="H139" s="8" t="inlineStr"/>
-      <c r="I139" s="6" t="inlineStr"/>
-      <c r="J139" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H139" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr"/>
@@ -7200,20 +7544,32 @@
       <c r="E140" s="6" t="inlineStr"/>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G140" s="6" t="inlineStr"/>
-      <c r="H140" s="8" t="inlineStr"/>
-      <c r="I140" s="6" t="inlineStr"/>
-      <c r="J140" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H140" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K140" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L140" s="6" t="inlineStr"/>
@@ -7238,20 +7594,32 @@
       <c r="E141" s="6" t="inlineStr"/>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G141" s="6" t="inlineStr"/>
-      <c r="H141" s="8" t="inlineStr"/>
-      <c r="I141" s="6" t="inlineStr"/>
-      <c r="J141" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G141" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H141" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr"/>
@@ -7276,20 +7644,32 @@
       <c r="E142" s="6" t="inlineStr"/>
       <c r="F142" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G142" s="6" t="inlineStr"/>
-      <c r="H142" s="8" t="inlineStr"/>
-      <c r="I142" s="6" t="inlineStr"/>
-      <c r="J142" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H142" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K142" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L142" s="6" t="inlineStr"/>
@@ -7314,20 +7694,32 @@
       <c r="E143" s="6" t="inlineStr"/>
       <c r="F143" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G143" s="6" t="inlineStr"/>
-      <c r="H143" s="8" t="inlineStr"/>
-      <c r="I143" s="6" t="inlineStr"/>
-      <c r="J143" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G143" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H143" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr"/>
@@ -7352,20 +7744,32 @@
       <c r="E144" s="6" t="inlineStr"/>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G144" s="6" t="inlineStr"/>
-      <c r="H144" s="8" t="inlineStr"/>
-      <c r="I144" s="6" t="inlineStr"/>
-      <c r="J144" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H144" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K144" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L144" s="6" t="inlineStr"/>
@@ -7390,20 +7794,32 @@
       <c r="E145" s="6" t="inlineStr"/>
       <c r="F145" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G145" s="6" t="inlineStr"/>
-      <c r="H145" s="8" t="inlineStr"/>
-      <c r="I145" s="6" t="inlineStr"/>
-      <c r="J145" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G145" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H145" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L145" s="6" t="inlineStr"/>
@@ -7428,20 +7844,32 @@
       <c r="E146" s="6" t="inlineStr"/>
       <c r="F146" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G146" s="6" t="inlineStr"/>
-      <c r="H146" s="8" t="inlineStr"/>
-      <c r="I146" s="6" t="inlineStr"/>
-      <c r="J146" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G146" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H146" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K146" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L146" s="6" t="inlineStr"/>
@@ -7466,20 +7894,32 @@
       <c r="E147" s="6" t="inlineStr"/>
       <c r="F147" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G147" s="6" t="inlineStr"/>
-      <c r="H147" s="8" t="inlineStr"/>
-      <c r="I147" s="6" t="inlineStr"/>
-      <c r="J147" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G147" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H147" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K147" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L147" s="6" t="inlineStr"/>
@@ -7504,20 +7944,32 @@
       <c r="E148" s="6" t="inlineStr"/>
       <c r="F148" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G148" s="6" t="inlineStr"/>
-      <c r="H148" s="8" t="inlineStr"/>
-      <c r="I148" s="6" t="inlineStr"/>
-      <c r="J148" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H148" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K148" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L148" s="6" t="inlineStr"/>
@@ -7542,20 +7994,32 @@
       <c r="E149" s="6" t="inlineStr"/>
       <c r="F149" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G149" s="6" t="inlineStr"/>
-      <c r="H149" s="8" t="inlineStr"/>
-      <c r="I149" s="6" t="inlineStr"/>
-      <c r="J149" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G149" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H149" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K149" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr"/>
@@ -7580,20 +8044,32 @@
       <c r="E150" s="6" t="inlineStr"/>
       <c r="F150" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G150" s="6" t="inlineStr"/>
-      <c r="H150" s="8" t="inlineStr"/>
-      <c r="I150" s="6" t="inlineStr"/>
-      <c r="J150" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G150" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H150" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K150" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L150" s="6" t="inlineStr"/>
@@ -7618,20 +8094,32 @@
       <c r="E151" s="6" t="inlineStr"/>
       <c r="F151" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G151" s="6" t="inlineStr"/>
-      <c r="H151" s="8" t="inlineStr"/>
-      <c r="I151" s="6" t="inlineStr"/>
-      <c r="J151" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G151" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H151" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr"/>
@@ -7656,20 +8144,32 @@
       <c r="E152" s="6" t="inlineStr"/>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G152" s="6" t="inlineStr"/>
-      <c r="H152" s="8" t="inlineStr"/>
-      <c r="I152" s="6" t="inlineStr"/>
-      <c r="J152" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H152" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K152" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L152" s="6" t="inlineStr"/>
@@ -7694,20 +8194,32 @@
       <c r="E153" s="6" t="inlineStr"/>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G153" s="6" t="inlineStr"/>
-      <c r="H153" s="8" t="inlineStr"/>
-      <c r="I153" s="6" t="inlineStr"/>
-      <c r="J153" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G153" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H153" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K153" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L153" s="6" t="inlineStr"/>
@@ -7732,20 +8244,32 @@
       <c r="E154" s="6" t="inlineStr"/>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G154" s="6" t="inlineStr"/>
-      <c r="H154" s="8" t="inlineStr"/>
-      <c r="I154" s="6" t="inlineStr"/>
-      <c r="J154" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H154" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K154" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L154" s="6" t="inlineStr"/>
@@ -7770,20 +8294,32 @@
       <c r="E155" s="6" t="inlineStr"/>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G155" s="6" t="inlineStr"/>
-      <c r="H155" s="8" t="inlineStr"/>
-      <c r="I155" s="6" t="inlineStr"/>
-      <c r="J155" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G155" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H155" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K155" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L155" s="6" t="inlineStr"/>
@@ -7808,20 +8344,32 @@
       <c r="E156" s="6" t="inlineStr"/>
       <c r="F156" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G156" s="6" t="inlineStr"/>
-      <c r="H156" s="8" t="inlineStr"/>
-      <c r="I156" s="6" t="inlineStr"/>
-      <c r="J156" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G156" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H156" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K156" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L156" s="6" t="inlineStr"/>
@@ -7846,20 +8394,32 @@
       <c r="E157" s="6" t="inlineStr"/>
       <c r="F157" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G157" s="6" t="inlineStr"/>
-      <c r="H157" s="8" t="inlineStr"/>
-      <c r="I157" s="6" t="inlineStr"/>
-      <c r="J157" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G157" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H157" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K157" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L157" s="6" t="inlineStr"/>
@@ -7884,20 +8444,32 @@
       <c r="E158" s="6" t="inlineStr"/>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G158" s="6" t="inlineStr"/>
-      <c r="H158" s="8" t="inlineStr"/>
-      <c r="I158" s="6" t="inlineStr"/>
-      <c r="J158" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G158" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H158" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K158" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L158" s="6" t="inlineStr"/>
@@ -7922,20 +8494,32 @@
       <c r="E159" s="6" t="inlineStr"/>
       <c r="F159" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G159" s="6" t="inlineStr"/>
-      <c r="H159" s="8" t="inlineStr"/>
-      <c r="I159" s="6" t="inlineStr"/>
-      <c r="J159" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G159" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H159" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr"/>
@@ -7960,20 +8544,32 @@
       <c r="E160" s="6" t="inlineStr"/>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G160" s="6" t="inlineStr"/>
-      <c r="H160" s="8" t="inlineStr"/>
-      <c r="I160" s="6" t="inlineStr"/>
-      <c r="J160" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H160" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K160" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L160" s="6" t="inlineStr"/>
@@ -7998,20 +8594,32 @@
       <c r="E161" s="6" t="inlineStr"/>
       <c r="F161" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G161" s="6" t="inlineStr"/>
-      <c r="H161" s="8" t="inlineStr"/>
-      <c r="I161" s="6" t="inlineStr"/>
-      <c r="J161" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G161" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H161" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L161" s="6" t="inlineStr"/>
@@ -8036,20 +8644,32 @@
       <c r="E162" s="6" t="inlineStr"/>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G162" s="6" t="inlineStr"/>
-      <c r="H162" s="8" t="inlineStr"/>
-      <c r="I162" s="6" t="inlineStr"/>
-      <c r="J162" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H162" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K162" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L162" s="6" t="inlineStr"/>
@@ -8074,20 +8694,32 @@
       <c r="E163" s="6" t="inlineStr"/>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G163" s="6" t="inlineStr"/>
-      <c r="H163" s="8" t="inlineStr"/>
-      <c r="I163" s="6" t="inlineStr"/>
-      <c r="J163" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G163" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H163" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K163" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L163" s="6" t="inlineStr"/>
@@ -8112,20 +8744,32 @@
       <c r="E164" s="6" t="inlineStr"/>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G164" s="6" t="inlineStr"/>
-      <c r="H164" s="8" t="inlineStr"/>
-      <c r="I164" s="6" t="inlineStr"/>
-      <c r="J164" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G164" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H164" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K164" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L164" s="6" t="inlineStr"/>
@@ -8163,7 +8807,7 @@
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>ЗАО «Арматурная Компания «ФОБОС» 8-800-700-62-60 info@fobosarm.ru</t>
+          <t>ЗАО «Арматурная Компания «ФОБОС» 8-800-700-62-60 info@fobosarm.ru | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr"/>
@@ -8188,20 +8832,32 @@
       <c r="E166" s="6" t="inlineStr"/>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G166" s="6" t="inlineStr"/>
-      <c r="H166" s="8" t="inlineStr"/>
-      <c r="I166" s="6" t="inlineStr"/>
-      <c r="J166" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G166" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H166" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K166" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L166" s="6" t="inlineStr"/>
@@ -8226,20 +8882,32 @@
       <c r="E167" s="6" t="inlineStr"/>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G167" s="6" t="inlineStr"/>
-      <c r="H167" s="8" t="inlineStr"/>
-      <c r="I167" s="6" t="inlineStr"/>
-      <c r="J167" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G167" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H167" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые 11с67п разборные (КШ.Р.) DN25-200; источник https://torgs.ru/industrial-products/440944/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr"/>
@@ -8264,20 +8932,32 @@
       <c r="E168" s="6" t="inlineStr"/>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G168" s="6" t="inlineStr"/>
-      <c r="H168" s="8" t="inlineStr"/>
-      <c r="I168" s="6" t="inlineStr"/>
-      <c r="J168" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G168" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H168" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K168" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые 11с67п разборные (КШ.Р.) DN25-200; источник https://torgs.ru/industrial-products/440944/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L168" s="6" t="inlineStr"/>
@@ -8302,20 +8982,32 @@
       <c r="E169" s="6" t="inlineStr"/>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G169" s="6" t="inlineStr"/>
-      <c r="H169" s="8" t="inlineStr"/>
-      <c r="I169" s="6" t="inlineStr"/>
-      <c r="J169" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G169" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H169" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
+      <c r="J169" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые 11с67п разборные (КШ.Р.) DN25-200; источник https://torgs.ru/industrial-products/440944/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr"/>
@@ -8340,20 +9032,32 @@
       <c r="E170" s="6" t="inlineStr"/>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G170" s="6" t="inlineStr"/>
-      <c r="H170" s="8" t="inlineStr"/>
-      <c r="I170" s="6" t="inlineStr"/>
-      <c r="J170" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G170" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H170" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K170" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые 11с67п разборные (КШ.Р.) DN25-200; источник https://torgs.ru/industrial-products/440944/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L170" s="6" t="inlineStr"/>
@@ -8378,20 +9082,32 @@
       <c r="E171" s="6" t="inlineStr"/>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G171" s="6" t="inlineStr"/>
-      <c r="H171" s="8" t="inlineStr"/>
-      <c r="I171" s="6" t="inlineStr"/>
-      <c r="J171" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G171" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H171" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="I171" s="6" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
+      <c r="J171" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K171" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые 11с67п разборные (КШ.Р.) DN25-200; источник https://torgs.ru/industrial-products/440944/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L171" s="6" t="inlineStr"/>
@@ -8416,20 +9132,32 @@
       <c r="E172" s="6" t="inlineStr"/>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G172" s="6" t="inlineStr"/>
-      <c r="H172" s="8" t="inlineStr"/>
-      <c r="I172" s="6" t="inlineStr"/>
-      <c r="J172" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G172" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H172" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="I172" s="6" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
+      <c r="J172" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K172" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые 11с67п разборные (КШ.Р.) DN25-200; источник https://torgs.ru/industrial-products/440944/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L172" s="6" t="inlineStr"/>
@@ -8454,20 +9182,32 @@
       <c r="E173" s="6" t="inlineStr"/>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G173" s="6" t="inlineStr"/>
-      <c r="H173" s="8" t="inlineStr"/>
-      <c r="I173" s="6" t="inlineStr"/>
-      <c r="J173" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G173" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H173" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
+      <c r="J173" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые 11с67п разборные (КШ.Р.) DN25-200; источник https://torgs.ru/industrial-products/440944/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L173" s="6" t="inlineStr"/>
@@ -8492,20 +9232,32 @@
       <c r="E174" s="6" t="inlineStr"/>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G174" s="6" t="inlineStr"/>
-      <c r="H174" s="8" t="inlineStr"/>
-      <c r="I174" s="6" t="inlineStr"/>
-      <c r="J174" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G174" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H174" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="I174" s="6" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K174" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые 11с67п разборные (КШ.Р.) DN25-200; источник https://torgs.ru/industrial-products/440944/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L174" s="6" t="inlineStr"/>
@@ -8530,20 +9282,32 @@
       <c r="E175" s="6" t="inlineStr"/>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G175" s="6" t="inlineStr"/>
-      <c r="H175" s="8" t="inlineStr"/>
-      <c r="I175" s="6" t="inlineStr"/>
-      <c r="J175" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G175" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H175" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
+      <c r="J175" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые 11с67п разборные (КШ.Р.) DN25-200; источник https://torgs.ru/industrial-products/440944/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L175" s="6" t="inlineStr"/>
@@ -8581,7 +9345,7 @@
       </c>
       <c r="K176" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ЛЗТА «Маршал» 8 (800) 301-20-50 info@lztamarshal.ru</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ЛЗТА «Маршал» 8 (800) 301-20-50 info@lztamarshal.ru | КШХ (химический) — у LD записи на такой кран не найдено; запросить у завода</t>
         </is>
       </c>
       <c r="L176" s="6" t="inlineStr"/>
@@ -8619,7 +9383,7 @@
       </c>
       <c r="K177" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ЛЗТА «Маршал» 8 (800) 301-20-50 info@lztamarshal.ru</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ЛЗТА «Маршал» 8 (800) 301-20-50 info@lztamarshal.ru | КШХ (химический) — у LD записи на такой кран не найдено; запросить у завода</t>
         </is>
       </c>
       <c r="L177" s="6" t="inlineStr"/>
@@ -8644,20 +9408,32 @@
       <c r="E178" s="6" t="inlineStr"/>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G178" s="6" t="inlineStr"/>
-      <c r="H178" s="8" t="inlineStr"/>
-      <c r="I178" s="6" t="inlineStr"/>
-      <c r="J178" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «Темпер»</t>
+        </is>
+      </c>
+      <c r="G178" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H178" s="8" t="inlineStr">
+        <is>
+          <t>10717439</t>
+        </is>
+      </c>
+      <c r="I178" s="6" t="inlineStr">
+        <is>
+          <t>23.09.2030</t>
+        </is>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K178" s="6" t="inlineStr">
         <is>
-          <t>ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru; ЛЗТА «Маршал» 8 (800) 301-20-50 info@lztamarshal.ru</t>
+          <t>Краны шаровые стальные TEMPER DN10-600 PN16-40; источник https://torgs.ru/industrial-products/444210/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L178" s="6" t="inlineStr"/>
@@ -8682,20 +9458,32 @@
       <c r="E179" s="6" t="inlineStr"/>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G179" s="6" t="inlineStr"/>
-      <c r="H179" s="8" t="inlineStr"/>
-      <c r="I179" s="6" t="inlineStr"/>
-      <c r="J179" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G179" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H179" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I179" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J179" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru; ЛЗТА «Маршал» 8 (800) 301-20-50 info@lztamarshal.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L179" s="6" t="inlineStr"/>
@@ -8720,20 +9508,32 @@
       <c r="E180" s="6" t="inlineStr"/>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G180" s="6" t="inlineStr"/>
-      <c r="H180" s="8" t="inlineStr"/>
-      <c r="I180" s="6" t="inlineStr"/>
-      <c r="J180" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ПромАрм»</t>
+        </is>
+      </c>
+      <c r="G180" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H180" s="8" t="inlineStr">
+        <is>
+          <t>10655456</t>
+        </is>
+      </c>
+      <c r="I180" s="6" t="inlineStr">
+        <is>
+          <t>24.07.2028</t>
+        </is>
+      </c>
+      <c r="J180" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K180" s="6" t="inlineStr">
         <is>
-          <t>ООО «ПромАрм» +7 (8412) 35-07-97 info@promarm.ru; АО «Пензтяжпромарматура» 8 800 444-00-28 (продажи) sales@ptpa.ru; АО «Пензенский арматурный завод» +7 (8412) 20-11-00 info@armpaz.ru</t>
+          <t>Затворы поворотные дисковые ПА; источник https://torgs.ru/industrial-products/387291/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L180" s="6" t="inlineStr"/>
@@ -8779,7 +9579,7 @@
       </c>
       <c r="K181" s="6" t="inlineStr">
         <is>
-          <t>Лидер-Энерго</t>
+          <t>Лидер-Энерго | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L181" s="6" t="inlineStr">
@@ -8829,7 +9629,7 @@
       </c>
       <c r="K182" s="6" t="inlineStr">
         <is>
-          <t>Лидер-Энерго</t>
+          <t>Лидер-Энерго | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L182" s="6" t="inlineStr">
@@ -8879,7 +9679,7 @@
       </c>
       <c r="K183" s="6" t="inlineStr">
         <is>
-          <t>Лидер-Энерго</t>
+          <t>Лидер-Энерго | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L183" s="6" t="inlineStr">
@@ -8912,7 +9712,7 @@
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="G184" s="6" t="inlineStr">
@@ -8920,16 +9720,24 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="H184" s="8" t="inlineStr"/>
-      <c r="I184" s="6" t="inlineStr"/>
-      <c r="J184" s="7" t="inlineStr">
-        <is>
-          <t>Российский производитель — запросить номер</t>
+      <c r="H184" s="8" t="inlineStr">
+        <is>
+          <t>10357202</t>
+        </is>
+      </c>
+      <c r="I184" s="6" t="inlineStr">
+        <is>
+          <t>15.03.2031</t>
+        </is>
+      </c>
+      <c r="J184" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K184" s="6" t="inlineStr">
         <is>
-          <t>ТД АДЛ (Гранвэл)</t>
+          <t>ЗПВС DN100; источник https://torgs.ru/industrial-products/100314/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L184" s="6" t="inlineStr">
@@ -8962,7 +9770,7 @@
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="G185" s="6" t="inlineStr">
@@ -8970,16 +9778,24 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="H185" s="8" t="inlineStr"/>
-      <c r="I185" s="6" t="inlineStr"/>
-      <c r="J185" s="7" t="inlineStr">
-        <is>
-          <t>Российский производитель — запросить номер</t>
+      <c r="H185" s="8" t="inlineStr">
+        <is>
+          <t>10357202</t>
+        </is>
+      </c>
+      <c r="I185" s="6" t="inlineStr">
+        <is>
+          <t>15.03.2031</t>
+        </is>
+      </c>
+      <c r="J185" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>ТД АДЛ (Гранвэл)</t>
+          <t>ЗПВС DN100; источник https://torgs.ru/industrial-products/100314/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L185" s="6" t="inlineStr">
@@ -9012,7 +9828,7 @@
       </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="G186" s="6" t="inlineStr">
@@ -9020,16 +9836,24 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="H186" s="8" t="inlineStr"/>
-      <c r="I186" s="6" t="inlineStr"/>
-      <c r="J186" s="7" t="inlineStr">
-        <is>
-          <t>Российский производитель — запросить номер</t>
+      <c r="H186" s="8" t="inlineStr">
+        <is>
+          <t>10837159</t>
+        </is>
+      </c>
+      <c r="I186" s="6" t="inlineStr">
+        <is>
+          <t>13.07.2029</t>
+        </is>
+      </c>
+      <c r="J186" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K186" s="6" t="inlineStr">
         <is>
-          <t>ТД АДЛ (Гранвэл)</t>
+          <t>Затворы Гранвэл DN25-500 PN до 1,6 — тип в записи не назван; источник https://torgs.ru/industrial-products/1038491/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L186" s="6" t="inlineStr">
@@ -9062,7 +9886,7 @@
       </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="G187" s="6" t="inlineStr">
@@ -9070,16 +9894,24 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="H187" s="8" t="inlineStr"/>
-      <c r="I187" s="6" t="inlineStr"/>
-      <c r="J187" s="7" t="inlineStr">
-        <is>
-          <t>Российский производитель — запросить номер</t>
+      <c r="H187" s="8" t="inlineStr">
+        <is>
+          <t>10837159</t>
+        </is>
+      </c>
+      <c r="I187" s="6" t="inlineStr">
+        <is>
+          <t>13.07.2029</t>
+        </is>
+      </c>
+      <c r="J187" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>ТД АДЛ (Гранвэл)</t>
+          <t>Затворы Гранвэл DN25-500 PN до 1,6 — тип в записи не назван; источник https://torgs.ru/industrial-products/1038491/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L187" s="6" t="inlineStr">
@@ -9112,7 +9944,7 @@
       </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="G188" s="6" t="inlineStr">
@@ -9120,16 +9952,24 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="H188" s="8" t="inlineStr"/>
-      <c r="I188" s="6" t="inlineStr"/>
-      <c r="J188" s="7" t="inlineStr">
-        <is>
-          <t>Российский производитель — запросить номер</t>
+      <c r="H188" s="8" t="inlineStr">
+        <is>
+          <t>10357205</t>
+        </is>
+      </c>
+      <c r="I188" s="6" t="inlineStr">
+        <is>
+          <t>15.03.2031</t>
+        </is>
+      </c>
+      <c r="J188" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K188" s="6" t="inlineStr">
         <is>
-          <t>ТД АДЛ (Гранвэл)</t>
+          <t>ЗПВС DN80; источник https://torgs.ru/industrial-products/100314/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L188" s="6" t="inlineStr">
@@ -9162,7 +10002,7 @@
       </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="G189" s="6" t="inlineStr">
@@ -9170,16 +10010,24 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="H189" s="8" t="inlineStr"/>
-      <c r="I189" s="6" t="inlineStr"/>
-      <c r="J189" s="7" t="inlineStr">
-        <is>
-          <t>Российский производитель — запросить номер</t>
+      <c r="H189" s="8" t="inlineStr">
+        <is>
+          <t>10837159</t>
+        </is>
+      </c>
+      <c r="I189" s="6" t="inlineStr">
+        <is>
+          <t>13.07.2029</t>
+        </is>
+      </c>
+      <c r="J189" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K189" s="6" t="inlineStr">
         <is>
-          <t>ТД АДЛ (Гранвэл)</t>
+          <t>Затворы Гранвэл DN25-500 PN до 1,6 — тип в записи не назван; источник https://torgs.ru/industrial-products/1038491/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L189" s="6" t="inlineStr">
@@ -9212,7 +10060,7 @@
       </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="G190" s="6" t="inlineStr">
@@ -9220,16 +10068,24 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="H190" s="8" t="inlineStr"/>
-      <c r="I190" s="6" t="inlineStr"/>
-      <c r="J190" s="7" t="inlineStr">
-        <is>
-          <t>Российский производитель — запросить номер</t>
+      <c r="H190" s="8" t="inlineStr">
+        <is>
+          <t>10837159</t>
+        </is>
+      </c>
+      <c r="I190" s="6" t="inlineStr">
+        <is>
+          <t>13.07.2029</t>
+        </is>
+      </c>
+      <c r="J190" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K190" s="6" t="inlineStr">
         <is>
-          <t>ТД АДЛ (Гранвэл)</t>
+          <t>Затворы Гранвэл DN25-500 PN до 1,6 — тип в записи не назван; источник https://torgs.ru/industrial-products/1038491/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L190" s="6" t="inlineStr">
@@ -9262,7 +10118,7 @@
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="G191" s="6" t="inlineStr">
@@ -9270,16 +10126,24 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="H191" s="8" t="inlineStr"/>
-      <c r="I191" s="6" t="inlineStr"/>
-      <c r="J191" s="7" t="inlineStr">
-        <is>
-          <t>Российский производитель — запросить номер</t>
+      <c r="H191" s="8" t="inlineStr">
+        <is>
+          <t>10357205</t>
+        </is>
+      </c>
+      <c r="I191" s="6" t="inlineStr">
+        <is>
+          <t>15.03.2031</t>
+        </is>
+      </c>
+      <c r="J191" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K191" s="6" t="inlineStr">
         <is>
-          <t>ТД АДЛ (Гранвэл)</t>
+          <t>ЗПВС DN80; источник https://torgs.ru/industrial-products/100314/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L191" s="6" t="inlineStr">
@@ -9312,7 +10176,7 @@
       </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="G192" s="6" t="inlineStr">
@@ -9320,16 +10184,24 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="H192" s="8" t="inlineStr"/>
-      <c r="I192" s="6" t="inlineStr"/>
-      <c r="J192" s="7" t="inlineStr">
-        <is>
-          <t>Российский производитель — запросить номер</t>
+      <c r="H192" s="8" t="inlineStr">
+        <is>
+          <t>10357198</t>
+        </is>
+      </c>
+      <c r="I192" s="6" t="inlineStr">
+        <is>
+          <t>15.03.2031</t>
+        </is>
+      </c>
+      <c r="J192" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K192" s="6" t="inlineStr">
         <is>
-          <t>ТД АДЛ (Гранвэл)</t>
+          <t>ЗПВС DN65; источник https://torgs.ru/industrial-products/100314/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L192" s="6" t="inlineStr">
@@ -9371,7 +10243,7 @@
       </c>
       <c r="K193" s="6" t="inlineStr">
         <is>
-          <t>ООО «Арма-Пром» +7 (4725) 469-470 (завод) zavod@saz-avangard.ru; АО «АБС ЗЭиМ Автоматизация» +7 (8352) 30-51-48 sales@zeim.ru; ООО «НПП «Промышленная автоматика» 8 (843) 558-25-28 info@promav.ru</t>
+          <t>ООО «Арма-Пром» +7 (4725) 469-470 (завод) zavod@saz-avangard.ru; АО «АБС ЗЭиМ Автоматизация» +7 (8352) 30-51-48 sales@zeim.ru; ООО «НПП «Промышленная автоматика» 8 (843) 558-25-28 info@promav.ru | Арма-Пром: записи 10232737/10232729/10232727 истекли 28.08.2026 (по зеркалу) — запросить новую запись у</t>
         </is>
       </c>
       <c r="L193" s="6" t="inlineStr"/>
@@ -9409,7 +10281,7 @@
       </c>
       <c r="K194" s="6" t="inlineStr">
         <is>
-          <t>ООО «ПКФ «ТЕРМ» +7 (927) 279-09-83 term1998@yandex.ru; ООО «Регул» +7 (499) 653-65-06 regyl21@mail.ru</t>
+          <t>ООО «ПКФ «ТЕРМ» +7 (927) 279-09-83 term1998@yandex.ru; ООО «Регул» +7 (499) 653-65-06 regyl21@mail.ru | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L194" s="6" t="inlineStr"/>
@@ -9455,7 +10327,7 @@
       </c>
       <c r="K195" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L195" s="6" t="inlineStr">
@@ -9505,7 +10377,7 @@
       </c>
       <c r="K196" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L196" s="6" t="inlineStr">
@@ -9555,7 +10427,7 @@
       </c>
       <c r="K197" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L197" s="6" t="inlineStr">
@@ -9584,20 +10456,32 @@
       <c r="E198" s="6" t="inlineStr"/>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G198" s="6" t="inlineStr"/>
-      <c r="H198" s="8" t="inlineStr"/>
-      <c r="I198" s="6" t="inlineStr"/>
-      <c r="J198" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
+        </is>
+      </c>
+      <c r="G198" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H198" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="I198" s="6" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
+      <c r="J198" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K198" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые латунные LD DN15-50 PN до 4,0 — изготовитель ЛД Прайд, не ЧСГС; источник https://torgs.ru/industrial-products/542786/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L198" s="6" t="inlineStr"/>
@@ -9622,20 +10506,32 @@
       <c r="E199" s="6" t="inlineStr"/>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G199" s="6" t="inlineStr"/>
-      <c r="H199" s="8" t="inlineStr"/>
-      <c r="I199" s="6" t="inlineStr"/>
-      <c r="J199" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
+        </is>
+      </c>
+      <c r="G199" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H199" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="I199" s="6" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
+      <c r="J199" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K199" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые латунные LD DN15-50 PN до 4,0 — изготовитель ЛД Прайд, не ЧСГС; источник https://torgs.ru/industrial-products/542786/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L199" s="6" t="inlineStr"/>
@@ -9660,20 +10556,32 @@
       <c r="E200" s="6" t="inlineStr"/>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G200" s="6" t="inlineStr"/>
-      <c r="H200" s="8" t="inlineStr"/>
-      <c r="I200" s="6" t="inlineStr"/>
-      <c r="J200" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
+        </is>
+      </c>
+      <c r="G200" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H200" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="I200" s="6" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
+      <c r="J200" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K200" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые латунные LD DN15-50 PN до 4,0 — изготовитель ЛД Прайд, не ЧСГС; источник https://torgs.ru/industrial-products/542786/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L200" s="6" t="inlineStr"/>
@@ -9698,20 +10606,32 @@
       <c r="E201" s="6" t="inlineStr"/>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G201" s="6" t="inlineStr"/>
-      <c r="H201" s="8" t="inlineStr"/>
-      <c r="I201" s="6" t="inlineStr"/>
-      <c r="J201" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
+        </is>
+      </c>
+      <c r="G201" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H201" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="I201" s="6" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
+      <c r="J201" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K201" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые латунные LD DN15-50 PN до 4,0 — изготовитель ЛД Прайд, не ЧСГС; источник https://torgs.ru/industrial-products/542786/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L201" s="6" t="inlineStr"/>
@@ -9736,20 +10656,32 @@
       <c r="E202" s="6" t="inlineStr"/>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G202" s="6" t="inlineStr"/>
-      <c r="H202" s="8" t="inlineStr"/>
-      <c r="I202" s="6" t="inlineStr"/>
-      <c r="J202" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
+        </is>
+      </c>
+      <c r="G202" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H202" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="I202" s="6" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
+      <c r="J202" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K202" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые латунные LD DN15-50 PN до 4,0 — изготовитель ЛД Прайд, не ЧСГС; источник https://torgs.ru/industrial-products/542786/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L202" s="6" t="inlineStr"/>
@@ -9774,20 +10706,32 @@
       <c r="E203" s="6" t="inlineStr"/>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G203" s="6" t="inlineStr"/>
-      <c r="H203" s="8" t="inlineStr"/>
-      <c r="I203" s="6" t="inlineStr"/>
-      <c r="J203" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G203" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H203" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I203" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J203" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K203" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L203" s="6" t="inlineStr"/>
@@ -9812,20 +10756,32 @@
       <c r="E204" s="6" t="inlineStr"/>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G204" s="6" t="inlineStr"/>
-      <c r="H204" s="8" t="inlineStr"/>
-      <c r="I204" s="6" t="inlineStr"/>
-      <c r="J204" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G204" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H204" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I204" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J204" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K204" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L204" s="6" t="inlineStr"/>
@@ -9850,20 +10806,32 @@
       <c r="E205" s="6" t="inlineStr"/>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G205" s="6" t="inlineStr"/>
-      <c r="H205" s="8" t="inlineStr"/>
-      <c r="I205" s="6" t="inlineStr"/>
-      <c r="J205" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G205" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H205" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I205" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J205" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K205" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L205" s="6" t="inlineStr"/>
@@ -9888,20 +10856,32 @@
       <c r="E206" s="6" t="inlineStr"/>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G206" s="6" t="inlineStr"/>
-      <c r="H206" s="8" t="inlineStr"/>
-      <c r="I206" s="6" t="inlineStr"/>
-      <c r="J206" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G206" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H206" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I206" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J206" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K206" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L206" s="6" t="inlineStr"/>
@@ -9926,20 +10906,32 @@
       <c r="E207" s="6" t="inlineStr"/>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G207" s="6" t="inlineStr"/>
-      <c r="H207" s="8" t="inlineStr"/>
-      <c r="I207" s="6" t="inlineStr"/>
-      <c r="J207" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G207" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H207" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I207" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J207" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K207" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L207" s="6" t="inlineStr"/>
@@ -9964,20 +10956,32 @@
       <c r="E208" s="6" t="inlineStr"/>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G208" s="6" t="inlineStr"/>
-      <c r="H208" s="8" t="inlineStr"/>
-      <c r="I208" s="6" t="inlineStr"/>
-      <c r="J208" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G208" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H208" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I208" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J208" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K208" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L208" s="6" t="inlineStr"/>
@@ -10002,20 +11006,32 @@
       <c r="E209" s="6" t="inlineStr"/>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G209" s="6" t="inlineStr"/>
-      <c r="H209" s="8" t="inlineStr"/>
-      <c r="I209" s="6" t="inlineStr"/>
-      <c r="J209" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G209" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H209" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I209" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J209" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K209" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L209" s="6" t="inlineStr"/>
@@ -10040,20 +11056,32 @@
       <c r="E210" s="6" t="inlineStr"/>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G210" s="6" t="inlineStr"/>
-      <c r="H210" s="8" t="inlineStr"/>
-      <c r="I210" s="6" t="inlineStr"/>
-      <c r="J210" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G210" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H210" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I210" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J210" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K210" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L210" s="6" t="inlineStr"/>
@@ -10078,20 +11106,32 @@
       <c r="E211" s="6" t="inlineStr"/>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G211" s="6" t="inlineStr"/>
-      <c r="H211" s="8" t="inlineStr"/>
-      <c r="I211" s="6" t="inlineStr"/>
-      <c r="J211" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G211" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H211" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I211" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J211" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K211" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L211" s="6" t="inlineStr"/>
@@ -10116,20 +11156,32 @@
       <c r="E212" s="6" t="inlineStr"/>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G212" s="6" t="inlineStr"/>
-      <c r="H212" s="8" t="inlineStr"/>
-      <c r="I212" s="6" t="inlineStr"/>
-      <c r="J212" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G212" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H212" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I212" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J212" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K212" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L212" s="6" t="inlineStr"/>
@@ -10175,7 +11227,7 @@
       </c>
       <c r="K213" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L213" s="6" t="inlineStr">
@@ -10225,7 +11277,7 @@
       </c>
       <c r="K214" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L214" s="6" t="inlineStr">
@@ -10275,7 +11327,7 @@
       </c>
       <c r="K215" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L215" s="6" t="inlineStr">
@@ -10325,7 +11377,7 @@
       </c>
       <c r="K216" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L216" s="6" t="inlineStr">
@@ -10375,7 +11427,7 @@
       </c>
       <c r="K217" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L217" s="6" t="inlineStr">
@@ -10425,7 +11477,7 @@
       </c>
       <c r="K218" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L218" s="6" t="inlineStr">
@@ -10475,7 +11527,7 @@
       </c>
       <c r="K219" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L219" s="6" t="inlineStr">
@@ -10525,7 +11577,7 @@
       </c>
       <c r="K220" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L220" s="6" t="inlineStr">
@@ -10575,7 +11627,7 @@
       </c>
       <c r="K221" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L221" s="6" t="inlineStr">
@@ -10625,7 +11677,7 @@
       </c>
       <c r="K222" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L222" s="6" t="inlineStr">
@@ -10725,7 +11777,7 @@
       </c>
       <c r="K224" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L224" s="6" t="inlineStr">
@@ -10775,7 +11827,7 @@
       </c>
       <c r="K225" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L225" s="6" t="inlineStr">
@@ -10825,7 +11877,7 @@
       </c>
       <c r="K226" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L226" s="6" t="inlineStr">
@@ -10875,7 +11927,7 @@
       </c>
       <c r="K227" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L227" s="6" t="inlineStr">
@@ -10925,7 +11977,7 @@
       </c>
       <c r="K228" s="6" t="inlineStr">
         <is>
-          <t>КИПИКА (прайс 01.10)</t>
+          <t>КИПИКА (прайс 01.10) | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L228" s="6" t="inlineStr">
@@ -10975,7 +12027,7 @@
       </c>
       <c r="K229" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L229" s="6" t="inlineStr">
@@ -11025,7 +12077,7 @@
       </c>
       <c r="K230" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L230" s="6" t="inlineStr">
@@ -11075,7 +12127,7 @@
       </c>
       <c r="K231" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L231" s="6" t="inlineStr">
@@ -11125,7 +12177,7 @@
       </c>
       <c r="K232" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L232" s="6" t="inlineStr">
@@ -11175,7 +12227,7 @@
       </c>
       <c r="K233" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L233" s="6" t="inlineStr">
@@ -11225,7 +12277,7 @@
       </c>
       <c r="K234" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L234" s="6" t="inlineStr">
@@ -11275,7 +12327,7 @@
       </c>
       <c r="K235" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L235" s="6" t="inlineStr">
@@ -11325,7 +12377,7 @@
       </c>
       <c r="K236" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L236" s="6" t="inlineStr">
@@ -11375,7 +12427,7 @@
       </c>
       <c r="K237" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L237" s="6" t="inlineStr">
@@ -11425,7 +12477,7 @@
       </c>
       <c r="K238" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L238" s="6" t="inlineStr">
@@ -11475,7 +12527,7 @@
       </c>
       <c r="K239" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L239" s="6" t="inlineStr">
@@ -11525,7 +12577,7 @@
       </c>
       <c r="K240" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L240" s="6" t="inlineStr">
@@ -11575,7 +12627,7 @@
       </c>
       <c r="K241" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L241" s="6" t="inlineStr">
@@ -11625,7 +12677,7 @@
       </c>
       <c r="K242" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L242" s="6" t="inlineStr">
@@ -11675,7 +12727,7 @@
       </c>
       <c r="K243" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L243" s="6" t="inlineStr">
@@ -11725,7 +12777,7 @@
       </c>
       <c r="K244" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L244" s="6" t="inlineStr">
@@ -11775,7 +12827,7 @@
       </c>
       <c r="K245" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L245" s="6" t="inlineStr">
@@ -11825,7 +12877,7 @@
       </c>
       <c r="K246" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L246" s="6" t="inlineStr">
@@ -11875,7 +12927,7 @@
       </c>
       <c r="K247" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L247" s="6" t="inlineStr">
@@ -11925,7 +12977,7 @@
       </c>
       <c r="K248" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L248" s="6" t="inlineStr">
@@ -11975,7 +13027,7 @@
       </c>
       <c r="K249" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L249" s="6" t="inlineStr">
@@ -12025,7 +13077,7 @@
       </c>
       <c r="K250" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L250" s="6" t="inlineStr">
@@ -12075,7 +13127,7 @@
       </c>
       <c r="K251" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L251" s="6" t="inlineStr">
@@ -12125,7 +13177,7 @@
       </c>
       <c r="K252" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L252" s="6" t="inlineStr">
@@ -12175,7 +13227,7 @@
       </c>
       <c r="K253" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L253" s="6" t="inlineStr">
@@ -12225,7 +13277,7 @@
       </c>
       <c r="K254" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L254" s="6" t="inlineStr">
@@ -12275,7 +13327,7 @@
       </c>
       <c r="K255" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L255" s="6" t="inlineStr">
@@ -12325,7 +13377,7 @@
       </c>
       <c r="K256" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L256" s="6" t="inlineStr">
@@ -12375,7 +13427,7 @@
       </c>
       <c r="K257" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L257" s="6" t="inlineStr">
@@ -12425,7 +13477,7 @@
       </c>
       <c r="K258" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L258" s="6" t="inlineStr">
@@ -12475,7 +13527,7 @@
       </c>
       <c r="K259" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | если изготовитель ЛМЗ — 10636782 (30ч6бр, до 15.05.2028); у БК-Арматуры уточнить завод</t>
         </is>
       </c>
       <c r="L259" s="6" t="inlineStr">
@@ -12525,7 +13577,7 @@
       </c>
       <c r="K260" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L260" s="6" t="inlineStr">
@@ -12575,7 +13627,7 @@
       </c>
       <c r="K261" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | если изготовитель ЛМЗ — 10636782 (30ч6бр, до 15.05.2028); у БК-Арматуры уточнить завод</t>
         </is>
       </c>
       <c r="L261" s="6" t="inlineStr">
@@ -12625,7 +13677,7 @@
       </c>
       <c r="K262" s="6" t="inlineStr">
         <is>
-          <t>КИПИКА (прайс 01.10)</t>
+          <t>КИПИКА (прайс 01.10) | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L262" s="6" t="inlineStr">
@@ -12654,20 +13706,32 @@
       <c r="E263" s="6" t="inlineStr"/>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G263" s="6" t="inlineStr"/>
-      <c r="H263" s="8" t="inlineStr"/>
-      <c r="I263" s="6" t="inlineStr"/>
-      <c r="J263" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
+        </is>
+      </c>
+      <c r="G263" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H263" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="I263" s="6" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
+      <c r="J263" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K263" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые латунные LD DN15-50 PN до 4,0 — изготовитель ЛД Прайд, не ЧСГС; источник https://torgs.ru/industrial-products/542786/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L263" s="6" t="inlineStr"/>
@@ -12692,20 +13756,32 @@
       <c r="E264" s="6" t="inlineStr"/>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G264" s="6" t="inlineStr"/>
-      <c r="H264" s="8" t="inlineStr"/>
-      <c r="I264" s="6" t="inlineStr"/>
-      <c r="J264" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
+        </is>
+      </c>
+      <c r="G264" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H264" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="I264" s="6" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
+      <c r="J264" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K264" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые латунные LD DN15-50 PN до 4,0 — изготовитель ЛД Прайд, не ЧСГС; источник https://torgs.ru/industrial-products/542786/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L264" s="6" t="inlineStr"/>
@@ -12730,20 +13806,32 @@
       <c r="E265" s="6" t="inlineStr"/>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G265" s="6" t="inlineStr"/>
-      <c r="H265" s="8" t="inlineStr"/>
-      <c r="I265" s="6" t="inlineStr"/>
-      <c r="J265" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
+        </is>
+      </c>
+      <c r="G265" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H265" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="I265" s="6" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
+      <c r="J265" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K265" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые латунные LD DN15-50 PN до 4,0 — изготовитель ЛД Прайд, не ЧСГС; источник https://torgs.ru/industrial-products/542786/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L265" s="6" t="inlineStr"/>
@@ -12768,20 +13856,32 @@
       <c r="E266" s="6" t="inlineStr"/>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G266" s="6" t="inlineStr"/>
-      <c r="H266" s="8" t="inlineStr"/>
-      <c r="I266" s="6" t="inlineStr"/>
-      <c r="J266" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
+        </is>
+      </c>
+      <c r="G266" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H266" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="I266" s="6" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
+      <c r="J266" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K266" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые латунные LD DN15-50 PN до 4,0 — изготовитель ЛД Прайд, не ЧСГС; источник https://torgs.ru/industrial-products/542786/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L266" s="6" t="inlineStr"/>
@@ -12806,20 +13906,32 @@
       <c r="E267" s="6" t="inlineStr"/>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G267" s="6" t="inlineStr"/>
-      <c r="H267" s="8" t="inlineStr"/>
-      <c r="I267" s="6" t="inlineStr"/>
-      <c r="J267" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
+        </is>
+      </c>
+      <c r="G267" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H267" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="I267" s="6" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
+      <c r="J267" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K267" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые латунные LD DN15-50 PN до 4,0 — изготовитель ЛД Прайд, не ЧСГС; источник https://torgs.ru/industrial-products/542786/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L267" s="6" t="inlineStr"/>
@@ -12844,20 +13956,32 @@
       <c r="E268" s="6" t="inlineStr"/>
       <c r="F268" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G268" s="6" t="inlineStr"/>
-      <c r="H268" s="8" t="inlineStr"/>
-      <c r="I268" s="6" t="inlineStr"/>
-      <c r="J268" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЛД Прайд» (ИНН 7449114775)</t>
+        </is>
+      </c>
+      <c r="G268" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H268" s="8" t="inlineStr">
+        <is>
+          <t>10826766</t>
+        </is>
+      </c>
+      <c r="I268" s="6" t="inlineStr">
+        <is>
+          <t>04.05.2031</t>
+        </is>
+      </c>
+      <c r="J268" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K268" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые латунные LD DN15-50 PN до 4,0 — изготовитель ЛД Прайд, не ЧСГС; источник https://torgs.ru/industrial-products/542786/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L268" s="6" t="inlineStr"/>
@@ -12882,20 +14006,32 @@
       <c r="E269" s="6" t="inlineStr"/>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G269" s="6" t="inlineStr"/>
-      <c r="H269" s="8" t="inlineStr"/>
-      <c r="I269" s="6" t="inlineStr"/>
-      <c r="J269" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G269" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H269" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I269" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J269" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K269" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L269" s="6" t="inlineStr"/>
@@ -12920,20 +14056,32 @@
       <c r="E270" s="6" t="inlineStr"/>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G270" s="6" t="inlineStr"/>
-      <c r="H270" s="8" t="inlineStr"/>
-      <c r="I270" s="6" t="inlineStr"/>
-      <c r="J270" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G270" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H270" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I270" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J270" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K270" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L270" s="6" t="inlineStr"/>
@@ -12958,20 +14106,32 @@
       <c r="E271" s="6" t="inlineStr"/>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G271" s="6" t="inlineStr"/>
-      <c r="H271" s="8" t="inlineStr"/>
-      <c r="I271" s="6" t="inlineStr"/>
-      <c r="J271" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G271" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H271" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I271" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J271" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K271" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L271" s="6" t="inlineStr"/>
@@ -12996,20 +14156,32 @@
       <c r="E272" s="6" t="inlineStr"/>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G272" s="6" t="inlineStr"/>
-      <c r="H272" s="8" t="inlineStr"/>
-      <c r="I272" s="6" t="inlineStr"/>
-      <c r="J272" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G272" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H272" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I272" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J272" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K272" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L272" s="6" t="inlineStr"/>
@@ -13034,20 +14206,32 @@
       <c r="E273" s="6" t="inlineStr"/>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G273" s="6" t="inlineStr"/>
-      <c r="H273" s="8" t="inlineStr"/>
-      <c r="I273" s="6" t="inlineStr"/>
-      <c r="J273" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G273" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H273" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I273" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J273" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K273" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L273" s="6" t="inlineStr"/>
@@ -13072,20 +14256,32 @@
       <c r="E274" s="6" t="inlineStr"/>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G274" s="6" t="inlineStr"/>
-      <c r="H274" s="8" t="inlineStr"/>
-      <c r="I274" s="6" t="inlineStr"/>
-      <c r="J274" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G274" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H274" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I274" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J274" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K274" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L274" s="6" t="inlineStr"/>
@@ -13110,20 +14306,32 @@
       <c r="E275" s="6" t="inlineStr"/>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G275" s="6" t="inlineStr"/>
-      <c r="H275" s="8" t="inlineStr"/>
-      <c r="I275" s="6" t="inlineStr"/>
-      <c r="J275" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G275" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H275" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I275" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J275" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K275" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L275" s="6" t="inlineStr"/>
@@ -13148,20 +14356,32 @@
       <c r="E276" s="6" t="inlineStr"/>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G276" s="6" t="inlineStr"/>
-      <c r="H276" s="8" t="inlineStr"/>
-      <c r="I276" s="6" t="inlineStr"/>
-      <c r="J276" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G276" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H276" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I276" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J276" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K276" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L276" s="6" t="inlineStr"/>
@@ -13186,20 +14406,32 @@
       <c r="E277" s="6" t="inlineStr"/>
       <c r="F277" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G277" s="6" t="inlineStr"/>
-      <c r="H277" s="8" t="inlineStr"/>
-      <c r="I277" s="6" t="inlineStr"/>
-      <c r="J277" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G277" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H277" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I277" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J277" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K277" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L277" s="6" t="inlineStr"/>
@@ -13224,20 +14456,32 @@
       <c r="E278" s="6" t="inlineStr"/>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G278" s="6" t="inlineStr"/>
-      <c r="H278" s="8" t="inlineStr"/>
-      <c r="I278" s="6" t="inlineStr"/>
-      <c r="J278" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G278" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H278" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I278" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J278" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K278" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L278" s="6" t="inlineStr"/>
@@ -13262,20 +14506,32 @@
       <c r="E279" s="6" t="inlineStr"/>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G279" s="6" t="inlineStr"/>
-      <c r="H279" s="8" t="inlineStr"/>
-      <c r="I279" s="6" t="inlineStr"/>
-      <c r="J279" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G279" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H279" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I279" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J279" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K279" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L279" s="6" t="inlineStr"/>
@@ -13300,20 +14556,32 @@
       <c r="E280" s="6" t="inlineStr"/>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G280" s="6" t="inlineStr"/>
-      <c r="H280" s="8" t="inlineStr"/>
-      <c r="I280" s="6" t="inlineStr"/>
-      <c r="J280" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G280" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H280" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I280" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J280" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K280" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L280" s="6" t="inlineStr"/>
@@ -13338,20 +14606,32 @@
       <c r="E281" s="6" t="inlineStr"/>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G281" s="6" t="inlineStr"/>
-      <c r="H281" s="8" t="inlineStr"/>
-      <c r="I281" s="6" t="inlineStr"/>
-      <c r="J281" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G281" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H281" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I281" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J281" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K281" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L281" s="6" t="inlineStr"/>
@@ -13376,20 +14656,32 @@
       <c r="E282" s="6" t="inlineStr"/>
       <c r="F282" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G282" s="6" t="inlineStr"/>
-      <c r="H282" s="8" t="inlineStr"/>
-      <c r="I282" s="6" t="inlineStr"/>
-      <c r="J282" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G282" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H282" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I282" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J282" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K282" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L282" s="6" t="inlineStr"/>
@@ -13414,20 +14706,32 @@
       <c r="E283" s="6" t="inlineStr"/>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G283" s="6" t="inlineStr"/>
-      <c r="H283" s="8" t="inlineStr"/>
-      <c r="I283" s="6" t="inlineStr"/>
-      <c r="J283" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G283" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H283" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I283" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J283" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K283" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L283" s="6" t="inlineStr"/>
@@ -13452,20 +14756,32 @@
       <c r="E284" s="6" t="inlineStr"/>
       <c r="F284" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G284" s="6" t="inlineStr"/>
-      <c r="H284" s="8" t="inlineStr"/>
-      <c r="I284" s="6" t="inlineStr"/>
-      <c r="J284" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G284" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H284" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I284" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J284" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K284" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L284" s="6" t="inlineStr"/>
@@ -13490,20 +14806,32 @@
       <c r="E285" s="6" t="inlineStr"/>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G285" s="6" t="inlineStr"/>
-      <c r="H285" s="8" t="inlineStr"/>
-      <c r="I285" s="6" t="inlineStr"/>
-      <c r="J285" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G285" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H285" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I285" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J285" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K285" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L285" s="6" t="inlineStr"/>
@@ -13528,20 +14856,32 @@
       <c r="E286" s="6" t="inlineStr"/>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G286" s="6" t="inlineStr"/>
-      <c r="H286" s="8" t="inlineStr"/>
-      <c r="I286" s="6" t="inlineStr"/>
-      <c r="J286" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G286" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H286" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I286" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J286" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K286" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L286" s="6" t="inlineStr"/>
@@ -13566,20 +14906,32 @@
       <c r="E287" s="6" t="inlineStr"/>
       <c r="F287" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G287" s="6" t="inlineStr"/>
-      <c r="H287" s="8" t="inlineStr"/>
-      <c r="I287" s="6" t="inlineStr"/>
-      <c r="J287" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G287" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H287" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I287" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J287" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K287" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L287" s="6" t="inlineStr"/>
@@ -13604,20 +14956,32 @@
       <c r="E288" s="6" t="inlineStr"/>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G288" s="6" t="inlineStr"/>
-      <c r="H288" s="8" t="inlineStr"/>
-      <c r="I288" s="6" t="inlineStr"/>
-      <c r="J288" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G288" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H288" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I288" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J288" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K288" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L288" s="6" t="inlineStr"/>
@@ -13642,20 +15006,32 @@
       <c r="E289" s="6" t="inlineStr"/>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G289" s="6" t="inlineStr"/>
-      <c r="H289" s="8" t="inlineStr"/>
-      <c r="I289" s="6" t="inlineStr"/>
-      <c r="J289" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G289" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H289" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I289" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J289" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K289" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L289" s="6" t="inlineStr"/>
@@ -13680,20 +15056,32 @@
       <c r="E290" s="6" t="inlineStr"/>
       <c r="F290" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G290" s="6" t="inlineStr"/>
-      <c r="H290" s="8" t="inlineStr"/>
-      <c r="I290" s="6" t="inlineStr"/>
-      <c r="J290" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G290" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H290" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I290" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J290" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K290" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L290" s="6" t="inlineStr"/>
@@ -13718,20 +15106,32 @@
       <c r="E291" s="6" t="inlineStr"/>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G291" s="6" t="inlineStr"/>
-      <c r="H291" s="8" t="inlineStr"/>
-      <c r="I291" s="6" t="inlineStr"/>
-      <c r="J291" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G291" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H291" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I291" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J291" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K291" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L291" s="6" t="inlineStr"/>
@@ -13756,20 +15156,32 @@
       <c r="E292" s="6" t="inlineStr"/>
       <c r="F292" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G292" s="6" t="inlineStr"/>
-      <c r="H292" s="8" t="inlineStr"/>
-      <c r="I292" s="6" t="inlineStr"/>
-      <c r="J292" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G292" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H292" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I292" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J292" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K292" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L292" s="6" t="inlineStr"/>
@@ -13794,20 +15206,32 @@
       <c r="E293" s="6" t="inlineStr"/>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G293" s="6" t="inlineStr"/>
-      <c r="H293" s="8" t="inlineStr"/>
-      <c r="I293" s="6" t="inlineStr"/>
-      <c r="J293" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G293" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H293" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I293" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J293" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K293" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L293" s="6" t="inlineStr"/>
@@ -13845,7 +15269,7 @@
       </c>
       <c r="K294" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ЛЗТА «Маршал» 8 (800) 301-20-50 info@lztamarshal.ru</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ЛЗТА «Маршал» 8 (800) 301-20-50 info@lztamarshal.ru | оригинал TEMPER — у ТЕМПЕР номер 10717439; у LD (аналог) запросить</t>
         </is>
       </c>
       <c r="L294" s="6" t="inlineStr"/>
@@ -13870,20 +15294,32 @@
       <c r="E295" s="6" t="inlineStr"/>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G295" s="6" t="inlineStr"/>
-      <c r="H295" s="8" t="inlineStr"/>
-      <c r="I295" s="6" t="inlineStr"/>
-      <c r="J295" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G295" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H295" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="I295" s="6" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
+      <c r="J295" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K295" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые 11с67п разборные (КШ.Р.) DN25-200; источник https://torgs.ru/industrial-products/440944/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L295" s="6" t="inlineStr"/>
@@ -13908,20 +15344,32 @@
       <c r="E296" s="6" t="inlineStr"/>
       <c r="F296" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G296" s="6" t="inlineStr"/>
-      <c r="H296" s="8" t="inlineStr"/>
-      <c r="I296" s="6" t="inlineStr"/>
-      <c r="J296" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G296" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H296" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="I296" s="6" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
+      <c r="J296" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K296" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые 11с67п разборные (КШ.Р.) DN25-200; источник https://torgs.ru/industrial-products/440944/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L296" s="6" t="inlineStr"/>
@@ -13946,20 +15394,32 @@
       <c r="E297" s="6" t="inlineStr"/>
       <c r="F297" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G297" s="6" t="inlineStr"/>
-      <c r="H297" s="8" t="inlineStr"/>
-      <c r="I297" s="6" t="inlineStr"/>
-      <c r="J297" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G297" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H297" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="I297" s="6" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
+      <c r="J297" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K297" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые 11с67п разборные (КШ.Р.) DN25-200; источник https://torgs.ru/industrial-products/440944/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L297" s="6" t="inlineStr"/>
@@ -13984,20 +15444,32 @@
       <c r="E298" s="6" t="inlineStr"/>
       <c r="F298" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G298" s="6" t="inlineStr"/>
-      <c r="H298" s="8" t="inlineStr"/>
-      <c r="I298" s="6" t="inlineStr"/>
-      <c r="J298" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G298" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H298" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="I298" s="6" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
+      <c r="J298" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K298" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые 11с67п разборные (КШ.Р.) DN25-200; источник https://torgs.ru/industrial-products/440944/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L298" s="6" t="inlineStr"/>
@@ -14022,20 +15494,32 @@
       <c r="E299" s="6" t="inlineStr"/>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G299" s="6" t="inlineStr"/>
-      <c r="H299" s="8" t="inlineStr"/>
-      <c r="I299" s="6" t="inlineStr"/>
-      <c r="J299" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G299" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H299" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="I299" s="6" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
+      <c r="J299" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K299" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые 11с67п разборные (КШ.Р.) DN25-200; источник https://torgs.ru/industrial-products/440944/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L299" s="6" t="inlineStr"/>
@@ -14060,20 +15544,32 @@
       <c r="E300" s="6" t="inlineStr"/>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G300" s="6" t="inlineStr"/>
-      <c r="H300" s="8" t="inlineStr"/>
-      <c r="I300" s="6" t="inlineStr"/>
-      <c r="J300" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G300" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H300" s="8" t="inlineStr">
+        <is>
+          <t>10714005</t>
+        </is>
+      </c>
+      <c r="I300" s="6" t="inlineStr">
+        <is>
+          <t>17.09.2028</t>
+        </is>
+      </c>
+      <c r="J300" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K300" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые 11с67п разборные (КШ.Р.) DN25-200; источник https://torgs.ru/industrial-products/440944/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L300" s="6" t="inlineStr"/>
@@ -14102,7 +15598,7 @@
       </c>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="G301" s="6" t="inlineStr">
@@ -14110,16 +15606,24 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="H301" s="8" t="inlineStr"/>
-      <c r="I301" s="6" t="inlineStr"/>
-      <c r="J301" s="7" t="inlineStr">
-        <is>
-          <t>Российский производитель — запросить номер</t>
+      <c r="H301" s="8" t="inlineStr">
+        <is>
+          <t>10357202</t>
+        </is>
+      </c>
+      <c r="I301" s="6" t="inlineStr">
+        <is>
+          <t>15.03.2031</t>
+        </is>
+      </c>
+      <c r="J301" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K301" s="6" t="inlineStr">
         <is>
-          <t>ТД АДЛ (Гранвэл)</t>
+          <t>ЗПВС DN100; источник https://torgs.ru/industrial-products/100314/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L301" s="6" t="inlineStr">
@@ -14152,7 +15656,7 @@
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="G302" s="6" t="inlineStr">
@@ -14160,16 +15664,24 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="H302" s="8" t="inlineStr"/>
-      <c r="I302" s="6" t="inlineStr"/>
-      <c r="J302" s="7" t="inlineStr">
-        <is>
-          <t>Российский производитель — запросить номер</t>
+      <c r="H302" s="8" t="inlineStr">
+        <is>
+          <t>10357205</t>
+        </is>
+      </c>
+      <c r="I302" s="6" t="inlineStr">
+        <is>
+          <t>15.03.2031</t>
+        </is>
+      </c>
+      <c r="J302" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K302" s="6" t="inlineStr">
         <is>
-          <t>ТД АДЛ (Гранвэл)</t>
+          <t>ЗПВС DN80; источник https://torgs.ru/industrial-products/100314/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L302" s="6" t="inlineStr">
@@ -14202,7 +15714,7 @@
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (Гранвэл)</t>
         </is>
       </c>
       <c r="G303" s="6" t="inlineStr">
@@ -14210,16 +15722,24 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="H303" s="8" t="inlineStr"/>
-      <c r="I303" s="6" t="inlineStr"/>
-      <c r="J303" s="7" t="inlineStr">
-        <is>
-          <t>Российский производитель — запросить номер</t>
+      <c r="H303" s="8" t="inlineStr">
+        <is>
+          <t>10357205</t>
+        </is>
+      </c>
+      <c r="I303" s="6" t="inlineStr">
+        <is>
+          <t>15.03.2031</t>
+        </is>
+      </c>
+      <c r="J303" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K303" s="6" t="inlineStr">
         <is>
-          <t>ТД АДЛ (Гранвэл)</t>
+          <t>ЗПВС DN80; источник https://torgs.ru/industrial-products/100314/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L303" s="6" t="inlineStr">
@@ -14261,7 +15781,7 @@
       </c>
       <c r="K304" s="6" t="inlineStr">
         <is>
-          <t>ТЕД Газовые системы 8-800-550-60-80 info@tedgas.ru (отдел продаж: retail@karldungs.ru)</t>
+          <t>ТЕД Газовые системы 8-800-550-60-80 info@tedgas.ru (отдел продаж: retail@karldungs.ru) | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L304" s="6" t="inlineStr"/>
@@ -14299,7 +15819,7 @@
       </c>
       <c r="K305" s="6" t="inlineStr">
         <is>
-          <t>АО «АБС ЗЭиМ Автоматизация» +7 (8352) 30-51-48 sales@zeim.ru; Фирменный магазин ESBE 8-800-333-12-09 info@esbeshop.ru</t>
+          <t>АО «АБС ЗЭиМ Автоматизация» +7 (8352) 30-51-48 sales@zeim.ru; Фирменный магазин ESBE 8-800-333-12-09 info@esbeshop.ru | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L305" s="6" t="inlineStr"/>
@@ -14345,7 +15865,7 @@
       </c>
       <c r="K306" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L306" s="6" t="inlineStr">
@@ -14374,20 +15894,32 @@
       <c r="E307" s="6" t="inlineStr"/>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G307" s="6" t="inlineStr"/>
-      <c r="H307" s="8" t="inlineStr"/>
-      <c r="I307" s="6" t="inlineStr"/>
-      <c r="J307" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G307" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H307" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I307" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J307" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K307" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L307" s="6" t="inlineStr"/>
@@ -14412,20 +15944,32 @@
       <c r="E308" s="6" t="inlineStr"/>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G308" s="6" t="inlineStr"/>
-      <c r="H308" s="8" t="inlineStr"/>
-      <c r="I308" s="6" t="inlineStr"/>
-      <c r="J308" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G308" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H308" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I308" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J308" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K308" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L308" s="6" t="inlineStr"/>
@@ -14450,20 +15994,32 @@
       <c r="E309" s="6" t="inlineStr"/>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G309" s="6" t="inlineStr"/>
-      <c r="H309" s="8" t="inlineStr"/>
-      <c r="I309" s="6" t="inlineStr"/>
-      <c r="J309" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G309" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H309" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I309" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J309" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K309" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L309" s="6" t="inlineStr"/>
@@ -14509,7 +16065,7 @@
       </c>
       <c r="K310" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта</t>
+          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
         </is>
       </c>
       <c r="L310" s="6" t="inlineStr">
@@ -14538,20 +16094,32 @@
       <c r="E311" s="6" t="inlineStr"/>
       <c r="F311" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G311" s="6" t="inlineStr"/>
-      <c r="H311" s="8" t="inlineStr"/>
-      <c r="I311" s="6" t="inlineStr"/>
-      <c r="J311" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G311" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H311" s="8" t="inlineStr">
+        <is>
+          <t>10657717</t>
+        </is>
+      </c>
+      <c r="I311" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J311" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K311" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ЛЗТА «Маршал» 8 (800) 301-20-50 info@lztamarshal.ru; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40 uzta@mail.ru</t>
+          <t>Краны шаровые DN10-1200 (09Г2С и нержавеющая сталь) — сверить исполнение; источник https://torgs.ru/industrial-products/389488/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L311" s="6" t="inlineStr"/>
@@ -14576,20 +16144,32 @@
       <c r="E312" s="6" t="inlineStr"/>
       <c r="F312" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G312" s="6" t="inlineStr"/>
-      <c r="H312" s="8" t="inlineStr"/>
-      <c r="I312" s="6" t="inlineStr"/>
-      <c r="J312" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G312" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H312" s="8" t="inlineStr">
+        <is>
+          <t>10657717</t>
+        </is>
+      </c>
+      <c r="I312" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J312" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K312" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ЛЗТА «Маршал» 8 (800) 301-20-50 info@lztamarshal.ru; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40 uzta@mail.ru</t>
+          <t>Краны шаровые DN10-1200 (09Г2С и нержавеющая сталь) — сверить исполнение; источник https://torgs.ru/industrial-products/389488/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L312" s="6" t="inlineStr"/>
@@ -14614,20 +16194,32 @@
       <c r="E313" s="6" t="inlineStr"/>
       <c r="F313" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G313" s="6" t="inlineStr"/>
-      <c r="H313" s="8" t="inlineStr"/>
-      <c r="I313" s="6" t="inlineStr"/>
-      <c r="J313" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G313" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H313" s="8" t="inlineStr">
+        <is>
+          <t>10657717</t>
+        </is>
+      </c>
+      <c r="I313" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J313" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K313" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ЛЗТА «Маршал» 8 (800) 301-20-50 info@lztamarshal.ru; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40 uzta@mail.ru</t>
+          <t>Краны шаровые DN10-1200 (09Г2С и нержавеющая сталь) — сверить исполнение; источник https://torgs.ru/industrial-products/389488/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L313" s="6" t="inlineStr"/>
@@ -14652,20 +16244,32 @@
       <c r="E314" s="6" t="inlineStr"/>
       <c r="F314" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G314" s="6" t="inlineStr"/>
-      <c r="H314" s="8" t="inlineStr"/>
-      <c r="I314" s="6" t="inlineStr"/>
-      <c r="J314" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G314" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H314" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I314" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J314" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K314" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L314" s="6" t="inlineStr"/>
@@ -14690,20 +16294,32 @@
       <c r="E315" s="6" t="inlineStr"/>
       <c r="F315" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G315" s="6" t="inlineStr"/>
-      <c r="H315" s="8" t="inlineStr"/>
-      <c r="I315" s="6" t="inlineStr"/>
-      <c r="J315" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G315" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H315" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I315" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J315" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K315" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L315" s="6" t="inlineStr"/>
@@ -14728,20 +16344,32 @@
       <c r="E316" s="6" t="inlineStr"/>
       <c r="F316" s="6" t="inlineStr">
         <is>
-          <t>не выбран</t>
-        </is>
-      </c>
-      <c r="G316" s="6" t="inlineStr"/>
-      <c r="H316" s="8" t="inlineStr"/>
-      <c r="I316" s="6" t="inlineStr"/>
-      <c r="J316" s="11" t="inlineStr">
-        <is>
-          <t>Поставщик не выбран</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» (ИНН 7451211335)</t>
+        </is>
+      </c>
+      <c r="G316" s="6" t="inlineStr">
+        <is>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H316" s="8" t="inlineStr">
+        <is>
+          <t>10655491</t>
+        </is>
+      </c>
+      <c r="I316" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2028</t>
+        </is>
+      </c>
+      <c r="J316" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K316" s="6" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47 office@chsgs.ru; ООО «ТЕМПЕР» +7 (3522) 22-88-88 temper@temper.ru; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89 info@uztpa.ru</t>
+          <t>Краны шаровые «LD» DN10-1200 — сверить исполнение (цельносварной); источник https://torgs.ru/industrial-products/387326/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L316" s="6" t="inlineStr"/>
@@ -14759,7 +16387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -14813,15 +16441,15 @@
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>ТД АДЛ (Гранвэл)</t>
+          <t>КИПИКА (прайс 01.10)</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>1.3/154, 1.3/155, 1.3/156, 1.3/157, 1.3/158, 1.3/159, 1.3/160, 1.3/161, 1.3/162, 1.6/89, 1.6/90, 1.6/91</t>
+          <t>1.3/39, 1.3/100, 1.6/16, 1.6/50</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -14833,58 +16461,18 @@
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>КИПИКА (прайс 01.10)</t>
+          <t>Лидер-Энерго</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>1.3/39, 1.3/100, 1.6/16, 1.6/50</t>
+          <t>1.3/151, 1.3/152, 1.3/153</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Добрый день! Для заявки в ПАО «Камчатскэнерго» (32616346943, нацрежим ПП 1875 — ограничение) просим по каждой позиции вашего счёта/КП указать: завод-изготовитель, страну происхождения, номер реестровой записи из реестра российской промышленной продукции (ПП 719) или евразийского реестра, срок действия записи, и приложить выписку из ГИСП. Позиции иностранного производства без записи в реестре — прошу заменить на российские аналоги.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Лидер-Энерго</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>1.3/151, 1.3/152, 1.3/153</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Добрый день! Для заявки в ПАО «Камчатскэнерго» (32616346943, нацрежим ПП 1875 — ограничение) просим по каждой позиции вашего счёта/КП указать: завод-изготовитель, страну происхождения, номер реестровой записи из реестра российской промышленной продукции (ПП 719) или евразийского реестра, срок действия записи, и приложить выписку из ГИСП. Позиции иностранного производства без записи в реестре — прошу заменить на российские аналоги.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Тулаэлектропривод</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>1.1/24</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Добрый день! Для заявки в ПАО «Камчатскэнерго» (32616346943, нацрежим ПП 1875 — ограничение) просим по каждой позиции вашего счёта/КП указать: завод-изготовитель, страну происхождения, номер реестровой записи из реестра российской промышленной продукции (ПП 719) или евразийского реестра, срок действия записи, и приложить выписку из ГИСП. Позиции иностранного производства без записи в реестре — прошу заменить на российские аналоги.</t>
         </is>

--- a/KAMCHATKA_REESTR_MPT.xlsx
+++ b/KAMCHATKA_REESTR_MPT.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Запрос номеров" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Все позиции (315)'!$A$1:$L$316</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Все позиции (315)'!$A$1:$M$316</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L316"/>
+  <dimension ref="A1:M316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -696,6 +696,7 @@
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="44" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="44" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customHeight="1">
@@ -759,6 +760,11 @@
           <t>Поставщик</t>
         </is>
       </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
+          <t>Российский завод с действующей записью (замена)</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="44" customHeight="1">
       <c r="A2" s="5" t="n">
@@ -809,6 +815,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод» — № 10329690 до 16.09.2030</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="5" t="n">
@@ -859,6 +870,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="44" customHeight="1">
       <c r="A4" s="5" t="n">
@@ -909,6 +925,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="44" customHeight="1">
       <c r="A5" s="5" t="n">
@@ -959,6 +980,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="5" t="n">
@@ -1007,6 +1033,11 @@
       <c r="L6" s="6" t="inlineStr">
         <is>
           <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
         </is>
       </c>
     </row>
@@ -1047,6 +1078,7 @@
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr"/>
+      <c r="M7" s="6" t="inlineStr"/>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="5" t="n">
@@ -1097,6 +1129,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="5" t="n">
@@ -1147,6 +1184,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="5" t="n">
@@ -1197,6 +1239,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="5" t="n">
@@ -1247,6 +1294,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="5" t="n">
@@ -1297,6 +1349,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="5" t="n">
@@ -1347,6 +1404,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="5" t="n">
@@ -1397,6 +1459,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="44" customHeight="1">
       <c r="A15" s="5" t="n">
@@ -1447,6 +1514,7 @@
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr"/>
+      <c r="M15" s="6" t="inlineStr"/>
     </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="5" t="n">
@@ -1497,6 +1565,7 @@
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr"/>
+      <c r="M16" s="6" t="inlineStr"/>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="5" t="n">
@@ -1547,6 +1616,7 @@
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr"/>
+      <c r="M17" s="6" t="inlineStr"/>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="5" t="n">
@@ -1597,6 +1667,7 @@
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr"/>
+      <c r="M18" s="6" t="inlineStr"/>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="5" t="n">
@@ -1647,6 +1718,7 @@
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr"/>
+      <c r="M19" s="6" t="inlineStr"/>
     </row>
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="5" t="n">
@@ -1697,6 +1769,7 @@
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr"/>
+      <c r="M20" s="6" t="inlineStr"/>
     </row>
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="5" t="n">
@@ -1747,6 +1820,7 @@
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr"/>
+      <c r="M21" s="6" t="inlineStr"/>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="5" t="n">
@@ -1797,6 +1871,7 @@
         </is>
       </c>
       <c r="L22" s="6" t="inlineStr"/>
+      <c r="M22" s="6" t="inlineStr"/>
     </row>
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="5" t="n">
@@ -1847,6 +1922,7 @@
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr"/>
+      <c r="M23" s="6" t="inlineStr"/>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="5" t="n">
@@ -1897,6 +1973,7 @@
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr"/>
+      <c r="M24" s="6" t="inlineStr"/>
     </row>
     <row r="25" ht="44" customHeight="1">
       <c r="A25" s="5" t="n">
@@ -1955,6 +2032,7 @@
           <t>Тулаэлектропривод</t>
         </is>
       </c>
+      <c r="M25" s="6" t="inlineStr"/>
     </row>
     <row r="26" ht="44" customHeight="1">
       <c r="A26" s="5" t="n">
@@ -2005,6 +2083,7 @@
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr"/>
+      <c r="M26" s="6" t="inlineStr"/>
     </row>
     <row r="27" ht="44" customHeight="1">
       <c r="A27" s="5" t="n">
@@ -2055,6 +2134,7 @@
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr"/>
+      <c r="M27" s="6" t="inlineStr"/>
     </row>
     <row r="28" ht="44" customHeight="1">
       <c r="A28" s="5" t="n">
@@ -2105,6 +2185,7 @@
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr"/>
+      <c r="M28" s="6" t="inlineStr"/>
     </row>
     <row r="29" ht="44" customHeight="1">
       <c r="A29" s="5" t="n">
@@ -2155,6 +2236,7 @@
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr"/>
+      <c r="M29" s="6" t="inlineStr"/>
     </row>
     <row r="30" ht="44" customHeight="1">
       <c r="A30" s="5" t="n">
@@ -2205,6 +2287,7 @@
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr"/>
+      <c r="M30" s="6" t="inlineStr"/>
     </row>
     <row r="31" ht="44" customHeight="1">
       <c r="A31" s="5" t="n">
@@ -2253,6 +2336,11 @@
       <c r="L31" s="6" t="inlineStr">
         <is>
           <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>АО «Энерготехномаш» — № 10870236 до 30.06.2031</t>
         </is>
       </c>
     </row>
@@ -2293,6 +2381,7 @@
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr"/>
+      <c r="M32" s="6" t="inlineStr"/>
     </row>
     <row r="33" ht="44" customHeight="1">
       <c r="A33" s="5" t="n">
@@ -2331,6 +2420,7 @@
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
+      <c r="M33" s="6" t="inlineStr"/>
     </row>
     <row r="34" ht="44" customHeight="1">
       <c r="A34" s="5" t="n">
@@ -2369,6 +2459,7 @@
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr"/>
+      <c r="M34" s="6" t="inlineStr"/>
     </row>
     <row r="35" ht="44" customHeight="1">
       <c r="A35" s="5" t="n">
@@ -2407,6 +2498,7 @@
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
+      <c r="M35" s="6" t="inlineStr"/>
     </row>
     <row r="36" ht="44" customHeight="1">
       <c r="A36" s="5" t="n">
@@ -2457,6 +2549,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>АО «Энерготехномаш» — № 10789125 до 30.06.2031</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="44" customHeight="1">
       <c r="A37" s="5" t="n">
@@ -2507,6 +2604,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>АО «Энерготехномаш» — № 10789125 до 30.06.2031</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="44" customHeight="1">
       <c r="A38" s="5" t="n">
@@ -2557,6 +2659,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>АО «Энерготехномаш» — № 10789125 до 30.06.2031</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="44" customHeight="1">
       <c r="A39" s="5" t="n">
@@ -2582,29 +2689,42 @@
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>уточнить у поставщика</t>
+          <t>АО «Энерготехномаш» (ИНН 0323085570)</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="inlineStr"/>
-      <c r="I39" s="6" t="inlineStr"/>
-      <c r="J39" s="9" t="inlineStr">
-        <is>
-          <t>Страна/завод неизвестны — уточнить</t>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>10789125</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2031</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
+          <t>Регуляторы давления, перепада давления, расхода, перепуска УРРД DN 15-300; PN 16-40; источник https://torgs.ru/industrial-products/717389/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr">
         <is>
           <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>АО «Энерготехномаш» — № 10789125 до 30.06.2031</t>
         </is>
       </c>
     </row>
@@ -2657,6 +2777,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>АО «Энерготехномаш» — № 10789125 до 30.06.2031</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="44" customHeight="1">
       <c r="A41" s="5" t="n">
@@ -2682,29 +2807,42 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>уточнить у поставщика</t>
+          <t>АО «Энерготехномаш» (ИНН 0323085570)</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr"/>
-      <c r="I41" s="6" t="inlineStr"/>
-      <c r="J41" s="9" t="inlineStr">
-        <is>
-          <t>Страна/завод неизвестны — уточнить</t>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>10789125</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2031</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
+          <t>Регуляторы давления, перепада давления, расхода, перепуска УРРД DN 15-300; PN 16-40; источник https://torgs.ru/industrial-products/717389/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
           <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>АО «Энерготехномаш» — № 10789125 до 30.06.2031</t>
         </is>
       </c>
     </row>
@@ -2732,29 +2870,42 @@
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>уточнить у поставщика</t>
+          <t>АО «Энерготехномаш» (ИНН 0323085570)</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr"/>
-      <c r="I42" s="6" t="inlineStr"/>
-      <c r="J42" s="9" t="inlineStr">
-        <is>
-          <t>Страна/завод неизвестны — уточнить</t>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>10789125</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>30.06.2031</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
+          <t>Регуляторы давления, перепада давления, расхода, перепуска УРРД DN 15-300; PN 16-40; источник https://torgs.ru/industrial-products/717389/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
           <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t>АО «Энерготехномаш» — № 10789125 до 30.06.2031</t>
         </is>
       </c>
     </row>
@@ -2807,6 +2958,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>АО «Энерготехномаш» — № 10789125 до 30.06.2031</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="5" t="n">
@@ -2857,6 +3013,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод» — № 10329682 до 16.09.2030</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="44" customHeight="1">
       <c r="A45" s="5" t="n">
@@ -2907,6 +3068,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M45" s="6" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод» — № 10329682 до 16.09.2030</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="44" customHeight="1">
       <c r="A46" s="5" t="n">
@@ -2957,6 +3123,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ» — № 10618658 до 17.03.2028</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="5" t="n">
@@ -3007,6 +3178,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M47" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ» — № 10618655 до 17.03.2028</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="44" customHeight="1">
       <c r="A48" s="5" t="n">
@@ -3057,6 +3233,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M48" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ» — № 10618657 до 17.03.2028</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="44" customHeight="1">
       <c r="A49" s="5" t="n">
@@ -3107,6 +3288,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M49" s="6" t="inlineStr">
+        <is>
+          <t>АО «Энергия» — № 10743786 до 08.12.2030</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="44" customHeight="1">
       <c r="A50" s="5" t="n">
@@ -3132,29 +3318,42 @@
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>Dendor — завод-изготовитель уточнить</t>
+          <t>АО «Энергия» (ИНН 7805499441)</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>уточнить</t>
-        </is>
-      </c>
-      <c r="H50" s="8" t="inlineStr"/>
-      <c r="I50" s="6" t="inlineStr"/>
-      <c r="J50" s="9" t="inlineStr">
-        <is>
-          <t>Страна/завод неизвестны — уточнить</t>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>10743786</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>08.12.2030</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
+          <t>Клапан обратный двухстворчатый межфланцевый тип 010C; источник https://torgs.ru/industrial-products/466955/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr">
         <is>
           <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="M50" s="6" t="inlineStr">
+        <is>
+          <t>АО «Энергия» — № 10743786 до 08.12.2030</t>
         </is>
       </c>
     </row>
@@ -3207,6 +3406,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M51" s="6" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод» — № 10329682 до 16.09.2030</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="44" customHeight="1">
       <c r="A52" s="5" t="n">
@@ -3232,7 +3436,7 @@
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>ООО «ТД АДЛ» (Гранвэл/Гранлок, производство Лыткарино)</t>
+          <t>ООО «Торговый Дом АДЛ» (ИНН 7718625072)</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
@@ -3240,21 +3444,34 @@
           <t>Россия</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr"/>
-      <c r="I52" s="6" t="inlineStr"/>
-      <c r="J52" s="7" t="inlineStr">
-        <is>
-          <t>Российский производитель — запросить номер</t>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>10618660</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>17.03.2028</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K52" s="6" t="inlineStr">
         <is>
-          <t>ДН.РУ (менеджеру, выставившему счета 819892/819896) — запросить завод-изготовитель, страну и № записи по каждой строке счёта | номер в открытых источниках не найден — запросить у завода</t>
+          <t>Клапаны обратные торговой марки «Гранлок", тип ЗОП , DN 150 мм , PN 16 бар»; источник https://torgs.ru/industrial-products/351411/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L52" s="6" t="inlineStr">
         <is>
           <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="M52" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ» — № 10618660 до 17.03.2028</t>
         </is>
       </c>
     </row>
@@ -3307,6 +3524,7 @@
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr"/>
+      <c r="M53" s="6" t="inlineStr"/>
     </row>
     <row r="54" ht="44" customHeight="1">
       <c r="A54" s="5" t="n">
@@ -3357,6 +3575,7 @@
         </is>
       </c>
       <c r="L54" s="6" t="inlineStr"/>
+      <c r="M54" s="6" t="inlineStr"/>
     </row>
     <row r="55" ht="44" customHeight="1">
       <c r="A55" s="5" t="n">
@@ -3407,6 +3626,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M55" s="6" t="inlineStr">
+        <is>
+          <t>нет: Не закрыто: 16ч42р (чугун, приёмный с сеткой, PN 0,25 МПа). Запись ПТЗ «Клапан обратный подъёмный» — PN 1,6–25 МПа (ниже 1,6 не покрывает); ПЗТА.КО — без DN/PN/материала в записи. Запасной: ПЗТА.</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="44" customHeight="1">
       <c r="A56" s="5" t="n">
@@ -3457,6 +3681,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M56" s="6" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод» — № 10329682 до 16.09.2030</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="44" customHeight="1">
       <c r="A57" s="5" t="n">
@@ -3507,6 +3736,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M57" s="6" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод» — № 10329682 до 16.09.2030</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="44" customHeight="1">
       <c r="A58" s="5" t="n">
@@ -3557,6 +3791,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M58" s="6" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод» — № 10329682 до 16.09.2030</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="44" customHeight="1">
       <c r="A59" s="5" t="n">
@@ -3607,6 +3846,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M59" s="6" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод» — № 10329682 до 16.09.2030</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="44" customHeight="1">
       <c r="A60" s="5" t="n">
@@ -3657,6 +3901,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M60" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ» — № 10618659 до 17.03.2028</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="44" customHeight="1">
       <c r="A61" s="5" t="n">
@@ -3705,6 +3954,11 @@
       <c r="L61" s="6" t="inlineStr">
         <is>
           <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="M61" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ» — № 10618660 до 17.03.2028</t>
         </is>
       </c>
     </row>
@@ -3745,6 +3999,7 @@
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr"/>
+      <c r="M62" s="6" t="inlineStr"/>
     </row>
     <row r="63" ht="44" customHeight="1">
       <c r="A63" s="5" t="n">
@@ -3783,6 +4038,7 @@
         </is>
       </c>
       <c r="L63" s="6" t="inlineStr"/>
+      <c r="M63" s="6" t="inlineStr"/>
     </row>
     <row r="64" ht="44" customHeight="1">
       <c r="A64" s="5" t="n">
@@ -3821,6 +4077,7 @@
         </is>
       </c>
       <c r="L64" s="6" t="inlineStr"/>
+      <c r="M64" s="6" t="inlineStr"/>
     </row>
     <row r="65" ht="44" customHeight="1">
       <c r="A65" s="5" t="n">
@@ -3871,6 +4128,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M65" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">нет: Не закрыто: нужен нержавеющий межфланцевый пружинный Ду150 Ру40. АО «Энергия» 010C и Гранлок CV16 — только PN16 (и чугун). Возможный запасной — «Восточная арматурная компания»: «Затворы обратные </t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="44" customHeight="1">
       <c r="A66" s="5" t="n">
@@ -3921,6 +4183,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M66" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ» — № 10535129 до 18.04.2027</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="44" customHeight="1">
       <c r="A67" s="5" t="n">
@@ -3971,6 +4238,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M67" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ» — № 10535148 до 18.04.2027</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="44" customHeight="1">
       <c r="A68" s="5" t="n">
@@ -4021,6 +4293,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M68" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ» — № 10535148 до 18.04.2027</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="44" customHeight="1">
       <c r="A69" s="5" t="n">
@@ -4069,6 +4346,11 @@
       <c r="L69" s="6" t="inlineStr">
         <is>
           <t>КИПИКА (прайс 01.10)</t>
+        </is>
+      </c>
+      <c r="M69" s="6" t="inlineStr">
+        <is>
+          <t>ООО «ЛД Прайд» — № 10826766 до 04.05.2031</t>
         </is>
       </c>
     </row>
@@ -4109,6 +4391,7 @@
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr"/>
+      <c r="M70" s="6" t="inlineStr"/>
     </row>
     <row r="71" ht="44" customHeight="1">
       <c r="A71" s="5" t="n">
@@ -4159,6 +4442,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M71" s="6" t="inlineStr">
+        <is>
+          <t>нет: Не найдено: в реестре (ОКПД2 28.14.13.110, 28.14.11.*) нет ни одной действующей записи на диафрагменные/мембранные (футерованные) клапаны ВДХ. Ближайшее — нет. Позицию закрыть нельзя без ЕАЭС-изг</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="44" customHeight="1">
       <c r="A72" s="5" t="n">
@@ -4209,6 +4497,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M72" s="6" t="inlineStr">
+        <is>
+          <t>нет: Не найдено: в реестре (ОКПД2 28.14.13.110, 28.14.11.*) нет ни одной действующей записи на диафрагменные/мембранные (футерованные) клапаны ВДХ. Ближайшее — нет. Позицию закрыть нельзя без ЕАЭС-изг</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="44" customHeight="1">
       <c r="A73" s="5" t="n">
@@ -4259,6 +4552,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M73" s="6" t="inlineStr">
+        <is>
+          <t>нет: Не найдено: в реестре (ОКПД2 28.14.13.110, 28.14.11.*) нет ни одной действующей записи на диафрагменные/мембранные (футерованные) клапаны ВДХ. Ближайшее — нет. Позицию закрыть нельзя без ЕАЭС-изг</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="44" customHeight="1">
       <c r="A74" s="5" t="n">
@@ -4307,6 +4605,11 @@
       <c r="L74" s="6" t="inlineStr">
         <is>
           <t>ДН.РУ</t>
+        </is>
+      </c>
+      <c r="M74" s="6" t="inlineStr">
+        <is>
+          <t>нет: Не найдено: в реестре (ОКПД2 28.14.13.110, 28.14.11.*) нет ни одной действующей записи на диафрагменные/мембранные (футерованные) клапаны ВДХ. Ближайшее — нет. Позицию закрыть нельзя без ЕАЭС-изг</t>
         </is>
       </c>
     </row>
@@ -4347,6 +4650,7 @@
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
+      <c r="M75" s="6" t="inlineStr"/>
     </row>
     <row r="76" ht="44" customHeight="1">
       <c r="A76" s="5" t="n">
@@ -4385,6 +4689,7 @@
         </is>
       </c>
       <c r="L76" s="6" t="inlineStr"/>
+      <c r="M76" s="6" t="inlineStr"/>
     </row>
     <row r="77" ht="44" customHeight="1">
       <c r="A77" s="5" t="n">
@@ -4423,6 +4728,7 @@
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr"/>
+      <c r="M77" s="6" t="inlineStr"/>
     </row>
     <row r="78" ht="44" customHeight="1">
       <c r="A78" s="5" t="n">
@@ -4473,6 +4779,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M78" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Бологовский арматурный завод» — № 10895023 до 24.08.2031</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="44" customHeight="1">
       <c r="A79" s="5" t="n">
@@ -4523,6 +4834,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M79" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Бологовский арматурный завод» — № 10895023 до 24.08.2031</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="44" customHeight="1">
       <c r="A80" s="5" t="n">
@@ -4573,6 +4889,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M80" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Бологовский арматурный завод» — № 10895023 до 24.08.2031</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="44" customHeight="1">
       <c r="A81" s="5" t="n">
@@ -4623,6 +4944,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M81" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Бологовский арматурный завод» — № 10895022 до 24.08.2031</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="44" customHeight="1">
       <c r="A82" s="5" t="n">
@@ -4673,6 +4999,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M82" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Бологовский арматурный завод» — № 10895022 до 24.08.2031</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="44" customHeight="1">
       <c r="A83" s="5" t="n">
@@ -4723,6 +5054,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M83" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Бологовский арматурный завод» — № 10895022 до 24.08.2031</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="44" customHeight="1">
       <c r="A84" s="5" t="n">
@@ -4773,6 +5109,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M84" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="44" customHeight="1">
       <c r="A85" s="5" t="n">
@@ -4823,6 +5164,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M85" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="44" customHeight="1">
       <c r="A86" s="5" t="n">
@@ -4873,6 +5219,7 @@
         </is>
       </c>
       <c r="L86" s="6" t="inlineStr"/>
+      <c r="M86" s="6" t="inlineStr"/>
     </row>
     <row r="87" ht="44" customHeight="1">
       <c r="A87" s="5" t="n">
@@ -4923,6 +5270,7 @@
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr"/>
+      <c r="M87" s="6" t="inlineStr"/>
     </row>
     <row r="88" ht="44" customHeight="1">
       <c r="A88" s="5" t="n">
@@ -4973,6 +5321,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M88" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="44" customHeight="1">
       <c r="A89" s="5" t="n">
@@ -5023,6 +5376,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M89" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="44" customHeight="1">
       <c r="A90" s="5" t="n">
@@ -5073,6 +5431,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M90" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="44" customHeight="1">
       <c r="A91" s="5" t="n">
@@ -5123,6 +5486,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M91" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="44" customHeight="1">
       <c r="A92" s="5" t="n">
@@ -5173,6 +5541,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M92" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="44" customHeight="1">
       <c r="A93" s="5" t="n">
@@ -5223,6 +5596,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M93" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="44" customHeight="1">
       <c r="A94" s="5" t="n">
@@ -5273,6 +5651,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M94" s="6" t="inlineStr">
+        <is>
+          <t>нет: Не найдено: на чугунные (СЧ/КЧ) запорные клапаны 15ч75п2 действующих записей в реестре нет (ОКПД2 28.14.13.110 — только стальные/латунные). Запасной вариант — стальной аналог ПТЗ (15с18п/15с22нж)</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="44" customHeight="1">
       <c r="A95" s="5" t="n">
@@ -5323,6 +5706,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M95" s="6" t="inlineStr">
+        <is>
+          <t>нет: Не найдено: на чугунные (СЧ/КЧ) запорные клапаны 15ч75п2 действующих записей в реестре нет (ОКПД2 28.14.13.110 — только стальные/латунные). Запасной вариант — стальной аналог ПТЗ (15с18п/15с22нж)</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="44" customHeight="1">
       <c r="A96" s="5" t="n">
@@ -5373,6 +5761,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M96" s="6" t="inlineStr">
+        <is>
+          <t>нет: Не найдено: на чугунные (СЧ/КЧ) запорные клапаны 15ч76п2 действующих записей в реестре нет (ОКПД2 28.14.13.110 — только стальные/латунные). Запасной вариант — стальной аналог ПТЗ (15с18п/15с22нж)</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="44" customHeight="1">
       <c r="A97" s="5" t="n">
@@ -5423,6 +5816,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M97" s="6" t="inlineStr">
+        <is>
+          <t>АО «Энерготехномаш» — № 10870236 до 30.06.2031</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="44" customHeight="1">
       <c r="A98" s="5" t="n">
@@ -5473,6 +5871,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M98" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="44" customHeight="1">
       <c r="A99" s="5" t="n">
@@ -5523,6 +5926,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M99" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="44" customHeight="1">
       <c r="A100" s="5" t="n">
@@ -5573,6 +5981,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M100" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="44" customHeight="1">
       <c r="A101" s="5" t="n">
@@ -5623,6 +6036,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M101" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="44" customHeight="1">
       <c r="A102" s="5" t="n">
@@ -5673,6 +6091,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M102" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="44" customHeight="1">
       <c r="A103" s="5" t="n">
@@ -5723,6 +6146,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M103" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="44" customHeight="1">
       <c r="A104" s="5" t="n">
@@ -5773,6 +6201,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M104" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="44" customHeight="1">
       <c r="A105" s="5" t="n">
@@ -5823,6 +6256,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M105" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="44" customHeight="1">
       <c r="A106" s="5" t="n">
@@ -5873,6 +6311,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M106" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="44" customHeight="1">
       <c r="A107" s="5" t="n">
@@ -5923,6 +6366,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M107" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="44" customHeight="1">
       <c r="A108" s="5" t="n">
@@ -5973,6 +6421,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M108" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="44" customHeight="1">
       <c r="A109" s="5" t="n">
@@ -6023,6 +6476,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M109" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="44" customHeight="1">
       <c r="A110" s="5" t="n">
@@ -6073,6 +6531,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M110" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="44" customHeight="1">
       <c r="A111" s="5" t="n">
@@ -6123,6 +6586,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M111" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="44" customHeight="1">
       <c r="A112" s="5" t="n">
@@ -6173,6 +6641,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M112" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="44" customHeight="1">
       <c r="A113" s="5" t="n">
@@ -6223,6 +6696,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M113" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="44" customHeight="1">
       <c r="A114" s="5" t="n">
@@ -6273,6 +6751,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M114" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="44" customHeight="1">
       <c r="A115" s="5" t="n">
@@ -6323,6 +6806,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M115" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="44" customHeight="1">
       <c r="A116" s="5" t="n">
@@ -6373,6 +6861,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M116" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="44" customHeight="1">
       <c r="A117" s="5" t="n">
@@ -6423,6 +6916,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M117" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="44" customHeight="1">
       <c r="A118" s="5" t="n">
@@ -6473,6 +6971,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M118" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="44" customHeight="1">
       <c r="A119" s="5" t="n">
@@ -6523,6 +7026,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M119" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="44" customHeight="1">
       <c r="A120" s="5" t="n">
@@ -6573,6 +7081,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M120" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="44" customHeight="1">
       <c r="A121" s="5" t="n">
@@ -6623,6 +7136,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M121" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="44" customHeight="1">
       <c r="A122" s="5" t="n">
@@ -6673,6 +7191,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M122" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="44" customHeight="1">
       <c r="A123" s="5" t="n">
@@ -6723,6 +7246,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M123" s="6" t="inlineStr">
+        <is>
+          <t>ОАО «Литейно-механический завод» — № 10636782 до 15.05.2028</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="44" customHeight="1">
       <c r="A124" s="5" t="n">
@@ -6773,6 +7301,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M124" s="6" t="inlineStr">
+        <is>
+          <t>ОАО «Литейно-механический завод» — № 10636782 до 15.05.2028</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="44" customHeight="1">
       <c r="A125" s="5" t="n">
@@ -6823,6 +7356,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M125" s="6" t="inlineStr">
+        <is>
+          <t>ОАО «Литейно-механический завод» — № 10636782 до 15.05.2028</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="44" customHeight="1">
       <c r="A126" s="5" t="n">
@@ -6873,6 +7411,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M126" s="6" t="inlineStr">
+        <is>
+          <t>ОАО «Литейно-механический завод» — № 10636782 до 15.05.2028</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="44" customHeight="1">
       <c r="A127" s="5" t="n">
@@ -6923,6 +7466,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M127" s="6" t="inlineStr">
+        <is>
+          <t>ОАО «Литейно-механический завод» — № 10636782 до 15.05.2028</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="44" customHeight="1">
       <c r="A128" s="5" t="n">
@@ -6973,6 +7521,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M128" s="6" t="inlineStr">
+        <is>
+          <t>ОАО «Литейно-механический завод» — № 10636782 до 15.05.2028</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="44" customHeight="1">
       <c r="A129" s="5" t="n">
@@ -7023,6 +7576,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M129" s="6" t="inlineStr">
+        <is>
+          <t>ОАО «Литейно-механический завод» — № 10636782 до 15.05.2028</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="44" customHeight="1">
       <c r="A130" s="5" t="n">
@@ -7073,6 +7631,11 @@
           <t>КИПИКА (прайс 01.10)</t>
         </is>
       </c>
+      <c r="M130" s="6" t="inlineStr">
+        <is>
+          <t>ООО «ЛД Прайд» — № 10826766 до 04.05.2031</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="44" customHeight="1">
       <c r="A131" s="5" t="n">
@@ -7123,6 +7686,7 @@
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr"/>
+      <c r="M131" s="6" t="inlineStr"/>
     </row>
     <row r="132" ht="44" customHeight="1">
       <c r="A132" s="5" t="n">
@@ -7173,6 +7737,7 @@
         </is>
       </c>
       <c r="L132" s="6" t="inlineStr"/>
+      <c r="M132" s="6" t="inlineStr"/>
     </row>
     <row r="133" ht="44" customHeight="1">
       <c r="A133" s="5" t="n">
@@ -7223,6 +7788,7 @@
         </is>
       </c>
       <c r="L133" s="6" t="inlineStr"/>
+      <c r="M133" s="6" t="inlineStr"/>
     </row>
     <row r="134" ht="44" customHeight="1">
       <c r="A134" s="5" t="n">
@@ -7273,6 +7839,7 @@
         </is>
       </c>
       <c r="L134" s="6" t="inlineStr"/>
+      <c r="M134" s="6" t="inlineStr"/>
     </row>
     <row r="135" ht="44" customHeight="1">
       <c r="A135" s="5" t="n">
@@ -7323,6 +7890,7 @@
         </is>
       </c>
       <c r="L135" s="6" t="inlineStr"/>
+      <c r="M135" s="6" t="inlineStr"/>
     </row>
     <row r="136" ht="44" customHeight="1">
       <c r="A136" s="5" t="n">
@@ -7373,6 +7941,7 @@
         </is>
       </c>
       <c r="L136" s="6" t="inlineStr"/>
+      <c r="M136" s="6" t="inlineStr"/>
     </row>
     <row r="137" ht="44" customHeight="1">
       <c r="A137" s="5" t="n">
@@ -7423,6 +7992,7 @@
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr"/>
+      <c r="M137" s="6" t="inlineStr"/>
     </row>
     <row r="138" ht="44" customHeight="1">
       <c r="A138" s="5" t="n">
@@ -7473,6 +8043,7 @@
         </is>
       </c>
       <c r="L138" s="6" t="inlineStr"/>
+      <c r="M138" s="6" t="inlineStr"/>
     </row>
     <row r="139" ht="44" customHeight="1">
       <c r="A139" s="5" t="n">
@@ -7523,6 +8094,7 @@
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr"/>
+      <c r="M139" s="6" t="inlineStr"/>
     </row>
     <row r="140" ht="44" customHeight="1">
       <c r="A140" s="5" t="n">
@@ -7573,6 +8145,7 @@
         </is>
       </c>
       <c r="L140" s="6" t="inlineStr"/>
+      <c r="M140" s="6" t="inlineStr"/>
     </row>
     <row r="141" ht="44" customHeight="1">
       <c r="A141" s="5" t="n">
@@ -7623,6 +8196,7 @@
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr"/>
+      <c r="M141" s="6" t="inlineStr"/>
     </row>
     <row r="142" ht="44" customHeight="1">
       <c r="A142" s="5" t="n">
@@ -7673,6 +8247,7 @@
         </is>
       </c>
       <c r="L142" s="6" t="inlineStr"/>
+      <c r="M142" s="6" t="inlineStr"/>
     </row>
     <row r="143" ht="44" customHeight="1">
       <c r="A143" s="5" t="n">
@@ -7723,6 +8298,7 @@
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr"/>
+      <c r="M143" s="6" t="inlineStr"/>
     </row>
     <row r="144" ht="44" customHeight="1">
       <c r="A144" s="5" t="n">
@@ -7773,6 +8349,7 @@
         </is>
       </c>
       <c r="L144" s="6" t="inlineStr"/>
+      <c r="M144" s="6" t="inlineStr"/>
     </row>
     <row r="145" ht="44" customHeight="1">
       <c r="A145" s="5" t="n">
@@ -7823,6 +8400,7 @@
         </is>
       </c>
       <c r="L145" s="6" t="inlineStr"/>
+      <c r="M145" s="6" t="inlineStr"/>
     </row>
     <row r="146" ht="44" customHeight="1">
       <c r="A146" s="5" t="n">
@@ -7873,6 +8451,7 @@
         </is>
       </c>
       <c r="L146" s="6" t="inlineStr"/>
+      <c r="M146" s="6" t="inlineStr"/>
     </row>
     <row r="147" ht="44" customHeight="1">
       <c r="A147" s="5" t="n">
@@ -7923,6 +8502,7 @@
         </is>
       </c>
       <c r="L147" s="6" t="inlineStr"/>
+      <c r="M147" s="6" t="inlineStr"/>
     </row>
     <row r="148" ht="44" customHeight="1">
       <c r="A148" s="5" t="n">
@@ -7973,6 +8553,7 @@
         </is>
       </c>
       <c r="L148" s="6" t="inlineStr"/>
+      <c r="M148" s="6" t="inlineStr"/>
     </row>
     <row r="149" ht="44" customHeight="1">
       <c r="A149" s="5" t="n">
@@ -8023,6 +8604,7 @@
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr"/>
+      <c r="M149" s="6" t="inlineStr"/>
     </row>
     <row r="150" ht="44" customHeight="1">
       <c r="A150" s="5" t="n">
@@ -8073,6 +8655,7 @@
         </is>
       </c>
       <c r="L150" s="6" t="inlineStr"/>
+      <c r="M150" s="6" t="inlineStr"/>
     </row>
     <row r="151" ht="44" customHeight="1">
       <c r="A151" s="5" t="n">
@@ -8123,6 +8706,7 @@
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr"/>
+      <c r="M151" s="6" t="inlineStr"/>
     </row>
     <row r="152" ht="44" customHeight="1">
       <c r="A152" s="5" t="n">
@@ -8173,6 +8757,7 @@
         </is>
       </c>
       <c r="L152" s="6" t="inlineStr"/>
+      <c r="M152" s="6" t="inlineStr"/>
     </row>
     <row r="153" ht="44" customHeight="1">
       <c r="A153" s="5" t="n">
@@ -8223,6 +8808,7 @@
         </is>
       </c>
       <c r="L153" s="6" t="inlineStr"/>
+      <c r="M153" s="6" t="inlineStr"/>
     </row>
     <row r="154" ht="44" customHeight="1">
       <c r="A154" s="5" t="n">
@@ -8273,6 +8859,7 @@
         </is>
       </c>
       <c r="L154" s="6" t="inlineStr"/>
+      <c r="M154" s="6" t="inlineStr"/>
     </row>
     <row r="155" ht="44" customHeight="1">
       <c r="A155" s="5" t="n">
@@ -8323,6 +8910,7 @@
         </is>
       </c>
       <c r="L155" s="6" t="inlineStr"/>
+      <c r="M155" s="6" t="inlineStr"/>
     </row>
     <row r="156" ht="44" customHeight="1">
       <c r="A156" s="5" t="n">
@@ -8373,6 +8961,7 @@
         </is>
       </c>
       <c r="L156" s="6" t="inlineStr"/>
+      <c r="M156" s="6" t="inlineStr"/>
     </row>
     <row r="157" ht="44" customHeight="1">
       <c r="A157" s="5" t="n">
@@ -8423,6 +9012,7 @@
         </is>
       </c>
       <c r="L157" s="6" t="inlineStr"/>
+      <c r="M157" s="6" t="inlineStr"/>
     </row>
     <row r="158" ht="44" customHeight="1">
       <c r="A158" s="5" t="n">
@@ -8473,6 +9063,7 @@
         </is>
       </c>
       <c r="L158" s="6" t="inlineStr"/>
+      <c r="M158" s="6" t="inlineStr"/>
     </row>
     <row r="159" ht="44" customHeight="1">
       <c r="A159" s="5" t="n">
@@ -8523,6 +9114,7 @@
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr"/>
+      <c r="M159" s="6" t="inlineStr"/>
     </row>
     <row r="160" ht="44" customHeight="1">
       <c r="A160" s="5" t="n">
@@ -8573,6 +9165,7 @@
         </is>
       </c>
       <c r="L160" s="6" t="inlineStr"/>
+      <c r="M160" s="6" t="inlineStr"/>
     </row>
     <row r="161" ht="44" customHeight="1">
       <c r="A161" s="5" t="n">
@@ -8623,6 +9216,7 @@
         </is>
       </c>
       <c r="L161" s="6" t="inlineStr"/>
+      <c r="M161" s="6" t="inlineStr"/>
     </row>
     <row r="162" ht="44" customHeight="1">
       <c r="A162" s="5" t="n">
@@ -8673,6 +9267,7 @@
         </is>
       </c>
       <c r="L162" s="6" t="inlineStr"/>
+      <c r="M162" s="6" t="inlineStr"/>
     </row>
     <row r="163" ht="44" customHeight="1">
       <c r="A163" s="5" t="n">
@@ -8723,6 +9318,7 @@
         </is>
       </c>
       <c r="L163" s="6" t="inlineStr"/>
+      <c r="M163" s="6" t="inlineStr"/>
     </row>
     <row r="164" ht="44" customHeight="1">
       <c r="A164" s="5" t="n">
@@ -8773,6 +9369,7 @@
         </is>
       </c>
       <c r="L164" s="6" t="inlineStr"/>
+      <c r="M164" s="6" t="inlineStr"/>
     </row>
     <row r="165" ht="44" customHeight="1">
       <c r="A165" s="5" t="n">
@@ -8811,6 +9408,7 @@
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr"/>
+      <c r="M165" s="6" t="inlineStr"/>
     </row>
     <row r="166" ht="44" customHeight="1">
       <c r="A166" s="5" t="n">
@@ -8861,6 +9459,7 @@
         </is>
       </c>
       <c r="L166" s="6" t="inlineStr"/>
+      <c r="M166" s="6" t="inlineStr"/>
     </row>
     <row r="167" ht="44" customHeight="1">
       <c r="A167" s="5" t="n">
@@ -8911,6 +9510,7 @@
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr"/>
+      <c r="M167" s="6" t="inlineStr"/>
     </row>
     <row r="168" ht="44" customHeight="1">
       <c r="A168" s="5" t="n">
@@ -8961,6 +9561,7 @@
         </is>
       </c>
       <c r="L168" s="6" t="inlineStr"/>
+      <c r="M168" s="6" t="inlineStr"/>
     </row>
     <row r="169" ht="44" customHeight="1">
       <c r="A169" s="5" t="n">
@@ -9011,6 +9612,7 @@
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr"/>
+      <c r="M169" s="6" t="inlineStr"/>
     </row>
     <row r="170" ht="44" customHeight="1">
       <c r="A170" s="5" t="n">
@@ -9061,6 +9663,7 @@
         </is>
       </c>
       <c r="L170" s="6" t="inlineStr"/>
+      <c r="M170" s="6" t="inlineStr"/>
     </row>
     <row r="171" ht="44" customHeight="1">
       <c r="A171" s="5" t="n">
@@ -9111,6 +9714,7 @@
         </is>
       </c>
       <c r="L171" s="6" t="inlineStr"/>
+      <c r="M171" s="6" t="inlineStr"/>
     </row>
     <row r="172" ht="44" customHeight="1">
       <c r="A172" s="5" t="n">
@@ -9161,6 +9765,7 @@
         </is>
       </c>
       <c r="L172" s="6" t="inlineStr"/>
+      <c r="M172" s="6" t="inlineStr"/>
     </row>
     <row r="173" ht="44" customHeight="1">
       <c r="A173" s="5" t="n">
@@ -9211,6 +9816,7 @@
         </is>
       </c>
       <c r="L173" s="6" t="inlineStr"/>
+      <c r="M173" s="6" t="inlineStr"/>
     </row>
     <row r="174" ht="44" customHeight="1">
       <c r="A174" s="5" t="n">
@@ -9261,6 +9867,7 @@
         </is>
       </c>
       <c r="L174" s="6" t="inlineStr"/>
+      <c r="M174" s="6" t="inlineStr"/>
     </row>
     <row r="175" ht="44" customHeight="1">
       <c r="A175" s="5" t="n">
@@ -9311,6 +9918,7 @@
         </is>
       </c>
       <c r="L175" s="6" t="inlineStr"/>
+      <c r="M175" s="6" t="inlineStr"/>
     </row>
     <row r="176" ht="44" customHeight="1">
       <c r="A176" s="5" t="n">
@@ -9349,6 +9957,7 @@
         </is>
       </c>
       <c r="L176" s="6" t="inlineStr"/>
+      <c r="M176" s="6" t="inlineStr"/>
     </row>
     <row r="177" ht="44" customHeight="1">
       <c r="A177" s="5" t="n">
@@ -9387,6 +9996,7 @@
         </is>
       </c>
       <c r="L177" s="6" t="inlineStr"/>
+      <c r="M177" s="6" t="inlineStr"/>
     </row>
     <row r="178" ht="44" customHeight="1">
       <c r="A178" s="5" t="n">
@@ -9437,6 +10047,7 @@
         </is>
       </c>
       <c r="L178" s="6" t="inlineStr"/>
+      <c r="M178" s="6" t="inlineStr"/>
     </row>
     <row r="179" ht="44" customHeight="1">
       <c r="A179" s="5" t="n">
@@ -9487,6 +10098,7 @@
         </is>
       </c>
       <c r="L179" s="6" t="inlineStr"/>
+      <c r="M179" s="6" t="inlineStr"/>
     </row>
     <row r="180" ht="44" customHeight="1">
       <c r="A180" s="5" t="n">
@@ -9537,6 +10149,7 @@
         </is>
       </c>
       <c r="L180" s="6" t="inlineStr"/>
+      <c r="M180" s="6" t="inlineStr"/>
     </row>
     <row r="181" ht="44" customHeight="1">
       <c r="A181" s="5" t="n">
@@ -9562,29 +10175,42 @@
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>уточнить у Лидер-Энерго (ЗДП по ТУ 28.14.13-012-09338969-2019)</t>
+          <t>ООО «Транс-Энерго» (ИНН 6324029755)</t>
         </is>
       </c>
       <c r="G181" s="6" t="inlineStr">
         <is>
-          <t>Россия (уточнить)</t>
-        </is>
-      </c>
-      <c r="H181" s="8" t="inlineStr"/>
-      <c r="I181" s="6" t="inlineStr"/>
-      <c r="J181" s="9" t="inlineStr">
-        <is>
-          <t>Страна/завод неизвестны — уточнить</t>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H181" s="8" t="inlineStr">
+        <is>
+          <t>10876723</t>
+        </is>
+      </c>
+      <c r="I181" s="6" t="inlineStr">
+        <is>
+          <t>08.07.2031</t>
+        </is>
+      </c>
+      <c r="J181" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K181" s="6" t="inlineStr">
         <is>
-          <t>Лидер-Энерго | номер в открытых источниках не найден — запросить у завода</t>
+          <t>Затвор поворотный дисковый типа ЗПД-150; источник https://torgs.ru/industrial-products/636746/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L181" s="6" t="inlineStr">
         <is>
           <t>Лидер-Энерго</t>
+        </is>
+      </c>
+      <c r="M181" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Транс-Энерго» — № 10876723 до 08.07.2031</t>
         </is>
       </c>
     </row>
@@ -9612,29 +10238,42 @@
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>уточнить у Лидер-Энерго (ЗДП по ТУ 28.14.13-012-09338969-2019)</t>
+          <t>ООО «Транс-Энерго» (ИНН 6324029755)</t>
         </is>
       </c>
       <c r="G182" s="6" t="inlineStr">
         <is>
-          <t>Россия (уточнить)</t>
-        </is>
-      </c>
-      <c r="H182" s="8" t="inlineStr"/>
-      <c r="I182" s="6" t="inlineStr"/>
-      <c r="J182" s="9" t="inlineStr">
-        <is>
-          <t>Страна/завод неизвестны — уточнить</t>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H182" s="8" t="inlineStr">
+        <is>
+          <t>10876719</t>
+        </is>
+      </c>
+      <c r="I182" s="6" t="inlineStr">
+        <is>
+          <t>08.07.2031</t>
+        </is>
+      </c>
+      <c r="J182" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K182" s="6" t="inlineStr">
         <is>
-          <t>Лидер-Энерго | номер в открытых источниках не найден — запросить у завода</t>
+          <t>Затвор поворотный дисковый типа ЗПД-50; источник https://torgs.ru/industrial-products/636750/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L182" s="6" t="inlineStr">
         <is>
           <t>Лидер-Энерго</t>
+        </is>
+      </c>
+      <c r="M182" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Транс-Энерго» — № 10876719 до 08.07.2031</t>
         </is>
       </c>
     </row>
@@ -9662,29 +10301,42 @@
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>уточнить у Лидер-Энерго (ЗДП по ТУ 28.14.13-012-09338969-2019)</t>
+          <t>ООО «Транс-Энерго» (ИНН 6324029755)</t>
         </is>
       </c>
       <c r="G183" s="6" t="inlineStr">
         <is>
-          <t>Россия (уточнить)</t>
-        </is>
-      </c>
-      <c r="H183" s="8" t="inlineStr"/>
-      <c r="I183" s="6" t="inlineStr"/>
-      <c r="J183" s="9" t="inlineStr">
-        <is>
-          <t>Страна/завод неизвестны — уточнить</t>
+          <t>Россия</t>
+        </is>
+      </c>
+      <c r="H183" s="8" t="inlineStr">
+        <is>
+          <t>10876720</t>
+        </is>
+      </c>
+      <c r="I183" s="6" t="inlineStr">
+        <is>
+          <t>08.07.2031</t>
+        </is>
+      </c>
+      <c r="J183" s="4" t="inlineStr">
+        <is>
+          <t>Номер есть</t>
         </is>
       </c>
       <c r="K183" s="6" t="inlineStr">
         <is>
-          <t>Лидер-Энерго | номер в открытых источниках не найден — запросить у завода</t>
+          <t>Затвор поворотный дисковый типа ЗПД-80; источник https://torgs.ru/industrial-products/636749/ — сверить с ГИСП</t>
         </is>
       </c>
       <c r="L183" s="6" t="inlineStr">
         <is>
           <t>Лидер-Энерго</t>
+        </is>
+      </c>
+      <c r="M183" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Транс-Энерго» — № 10876720 до 08.07.2031</t>
         </is>
       </c>
     </row>
@@ -9745,6 +10397,7 @@
           <t>ТД АДЛ (Гранвэл)</t>
         </is>
       </c>
+      <c r="M184" s="6" t="inlineStr"/>
     </row>
     <row r="185" ht="44" customHeight="1">
       <c r="A185" s="5" t="n">
@@ -9803,6 +10456,7 @@
           <t>ТД АДЛ (Гранвэл)</t>
         </is>
       </c>
+      <c r="M185" s="6" t="inlineStr"/>
     </row>
     <row r="186" ht="44" customHeight="1">
       <c r="A186" s="5" t="n">
@@ -9861,6 +10515,7 @@
           <t>ТД АДЛ (Гранвэл)</t>
         </is>
       </c>
+      <c r="M186" s="6" t="inlineStr"/>
     </row>
     <row r="187" ht="44" customHeight="1">
       <c r="A187" s="5" t="n">
@@ -9919,6 +10574,7 @@
           <t>ТД АДЛ (Гранвэл)</t>
         </is>
       </c>
+      <c r="M187" s="6" t="inlineStr"/>
     </row>
     <row r="188" ht="44" customHeight="1">
       <c r="A188" s="5" t="n">
@@ -9977,6 +10633,7 @@
           <t>ТД АДЛ (Гранвэл)</t>
         </is>
       </c>
+      <c r="M188" s="6" t="inlineStr"/>
     </row>
     <row r="189" ht="44" customHeight="1">
       <c r="A189" s="5" t="n">
@@ -10035,6 +10692,7 @@
           <t>ТД АДЛ (Гранвэл)</t>
         </is>
       </c>
+      <c r="M189" s="6" t="inlineStr"/>
     </row>
     <row r="190" ht="44" customHeight="1">
       <c r="A190" s="5" t="n">
@@ -10093,6 +10751,7 @@
           <t>ТД АДЛ (Гранвэл)</t>
         </is>
       </c>
+      <c r="M190" s="6" t="inlineStr"/>
     </row>
     <row r="191" ht="44" customHeight="1">
       <c r="A191" s="5" t="n">
@@ -10151,6 +10810,7 @@
           <t>ТД АДЛ (Гранвэл)</t>
         </is>
       </c>
+      <c r="M191" s="6" t="inlineStr"/>
     </row>
     <row r="192" ht="44" customHeight="1">
       <c r="A192" s="5" t="n">
@@ -10209,6 +10869,7 @@
           <t>ТД АДЛ (Гранвэл)</t>
         </is>
       </c>
+      <c r="M192" s="6" t="inlineStr"/>
     </row>
     <row r="193" ht="44" customHeight="1">
       <c r="A193" s="5" t="n">
@@ -10247,6 +10908,7 @@
         </is>
       </c>
       <c r="L193" s="6" t="inlineStr"/>
+      <c r="M193" s="6" t="inlineStr"/>
     </row>
     <row r="194" ht="44" customHeight="1">
       <c r="A194" s="5" t="n">
@@ -10285,6 +10947,7 @@
         </is>
       </c>
       <c r="L194" s="6" t="inlineStr"/>
+      <c r="M194" s="6" t="inlineStr"/>
     </row>
     <row r="195" ht="44" customHeight="1">
       <c r="A195" s="5" t="n">
@@ -10335,6 +10998,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M195" s="6" t="inlineStr">
+        <is>
+          <t>нет: Не найдено: на чугунные (СЧ/КЧ) запорные клапаны 15кч18п действующих записей в реестре нет (ОКПД2 28.14.13.110 — только стальные/латунные). Запасной вариант — стальной аналог ПТЗ (15с18п/15с22нж)</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="44" customHeight="1">
       <c r="A196" s="5" t="n">
@@ -10385,6 +11053,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M196" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="44" customHeight="1">
       <c r="A197" s="5" t="n">
@@ -10435,6 +11108,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M197" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="44" customHeight="1">
       <c r="A198" s="5" t="n">
@@ -10485,6 +11163,7 @@
         </is>
       </c>
       <c r="L198" s="6" t="inlineStr"/>
+      <c r="M198" s="6" t="inlineStr"/>
     </row>
     <row r="199" ht="44" customHeight="1">
       <c r="A199" s="5" t="n">
@@ -10535,6 +11214,7 @@
         </is>
       </c>
       <c r="L199" s="6" t="inlineStr"/>
+      <c r="M199" s="6" t="inlineStr"/>
     </row>
     <row r="200" ht="44" customHeight="1">
       <c r="A200" s="5" t="n">
@@ -10585,6 +11265,7 @@
         </is>
       </c>
       <c r="L200" s="6" t="inlineStr"/>
+      <c r="M200" s="6" t="inlineStr"/>
     </row>
     <row r="201" ht="44" customHeight="1">
       <c r="A201" s="5" t="n">
@@ -10635,6 +11316,7 @@
         </is>
       </c>
       <c r="L201" s="6" t="inlineStr"/>
+      <c r="M201" s="6" t="inlineStr"/>
     </row>
     <row r="202" ht="44" customHeight="1">
       <c r="A202" s="5" t="n">
@@ -10685,6 +11367,7 @@
         </is>
       </c>
       <c r="L202" s="6" t="inlineStr"/>
+      <c r="M202" s="6" t="inlineStr"/>
     </row>
     <row r="203" ht="44" customHeight="1">
       <c r="A203" s="5" t="n">
@@ -10735,6 +11418,7 @@
         </is>
       </c>
       <c r="L203" s="6" t="inlineStr"/>
+      <c r="M203" s="6" t="inlineStr"/>
     </row>
     <row r="204" ht="44" customHeight="1">
       <c r="A204" s="5" t="n">
@@ -10785,6 +11469,7 @@
         </is>
       </c>
       <c r="L204" s="6" t="inlineStr"/>
+      <c r="M204" s="6" t="inlineStr"/>
     </row>
     <row r="205" ht="44" customHeight="1">
       <c r="A205" s="5" t="n">
@@ -10835,6 +11520,7 @@
         </is>
       </c>
       <c r="L205" s="6" t="inlineStr"/>
+      <c r="M205" s="6" t="inlineStr"/>
     </row>
     <row r="206" ht="44" customHeight="1">
       <c r="A206" s="5" t="n">
@@ -10885,6 +11571,7 @@
         </is>
       </c>
       <c r="L206" s="6" t="inlineStr"/>
+      <c r="M206" s="6" t="inlineStr"/>
     </row>
     <row r="207" ht="44" customHeight="1">
       <c r="A207" s="5" t="n">
@@ -10935,6 +11622,7 @@
         </is>
       </c>
       <c r="L207" s="6" t="inlineStr"/>
+      <c r="M207" s="6" t="inlineStr"/>
     </row>
     <row r="208" ht="44" customHeight="1">
       <c r="A208" s="5" t="n">
@@ -10985,6 +11673,7 @@
         </is>
       </c>
       <c r="L208" s="6" t="inlineStr"/>
+      <c r="M208" s="6" t="inlineStr"/>
     </row>
     <row r="209" ht="44" customHeight="1">
       <c r="A209" s="5" t="n">
@@ -11035,6 +11724,7 @@
         </is>
       </c>
       <c r="L209" s="6" t="inlineStr"/>
+      <c r="M209" s="6" t="inlineStr"/>
     </row>
     <row r="210" ht="44" customHeight="1">
       <c r="A210" s="5" t="n">
@@ -11085,6 +11775,7 @@
         </is>
       </c>
       <c r="L210" s="6" t="inlineStr"/>
+      <c r="M210" s="6" t="inlineStr"/>
     </row>
     <row r="211" ht="44" customHeight="1">
       <c r="A211" s="5" t="n">
@@ -11135,6 +11826,7 @@
         </is>
       </c>
       <c r="L211" s="6" t="inlineStr"/>
+      <c r="M211" s="6" t="inlineStr"/>
     </row>
     <row r="212" ht="44" customHeight="1">
       <c r="A212" s="5" t="n">
@@ -11185,6 +11877,7 @@
         </is>
       </c>
       <c r="L212" s="6" t="inlineStr"/>
+      <c r="M212" s="6" t="inlineStr"/>
     </row>
     <row r="213" ht="44" customHeight="1">
       <c r="A213" s="5" t="n">
@@ -11235,6 +11928,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M213" s="6" t="inlineStr">
+        <is>
+          <t>АО «Энерготехномаш» — № 10870236 до 30.06.2031</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="44" customHeight="1">
       <c r="A214" s="5" t="n">
@@ -11285,6 +11983,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M214" s="6" t="inlineStr">
+        <is>
+          <t>АО «Энерготехномаш» — № 10870236 до 30.06.2031</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="44" customHeight="1">
       <c r="A215" s="5" t="n">
@@ -11335,6 +12038,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M215" s="6" t="inlineStr">
+        <is>
+          <t>АО «Энерготехномаш» — № 10789125 до 30.06.2031</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="44" customHeight="1">
       <c r="A216" s="5" t="n">
@@ -11385,6 +12093,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M216" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ» — № 10618658 до 17.03.2028</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="44" customHeight="1">
       <c r="A217" s="5" t="n">
@@ -11435,6 +12148,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M217" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ» — № 10618655 до 17.03.2028</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="44" customHeight="1">
       <c r="A218" s="5" t="n">
@@ -11485,6 +12203,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M218" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Торговый Дом АДЛ» — № 10618657 до 17.03.2028</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="44" customHeight="1">
       <c r="A219" s="5" t="n">
@@ -11535,6 +12258,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M219" s="6" t="inlineStr">
+        <is>
+          <t>АО «Энергия» — № 10743786 до 08.12.2030</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="44" customHeight="1">
       <c r="A220" s="5" t="n">
@@ -11585,6 +12313,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M220" s="6" t="inlineStr">
+        <is>
+          <t>АО «Энергия» — № 10743786 до 08.12.2030</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="44" customHeight="1">
       <c r="A221" s="5" t="n">
@@ -11635,6 +12368,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M221" s="6" t="inlineStr">
+        <is>
+          <t>АО «Энергия» — № 10743786 до 08.12.2030</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="44" customHeight="1">
       <c r="A222" s="5" t="n">
@@ -11685,6 +12423,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M222" s="6" t="inlineStr">
+        <is>
+          <t>ООО ПКФ «Экс-Форма» — № 10538896 до 22.05.2027</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="44" customHeight="1">
       <c r="A223" s="5" t="n">
@@ -11735,6 +12478,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M223" s="6" t="inlineStr">
+        <is>
+          <t>нет: Не закрыто точно: 17с11нж Ду25 со штуцерно-торцевым присоединением в реестре не найден. Ближайшее — СППК4Р БАЗ DN25 (фланцевый) — другое присоединение.</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="44" customHeight="1">
       <c r="A224" s="5" t="n">
@@ -11785,6 +12533,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M224" s="6" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод» — № 10329690 до 16.09.2030</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="44" customHeight="1">
       <c r="A225" s="5" t="n">
@@ -11835,6 +12588,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M225" s="6" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод» — № 10329690 до 16.09.2030</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="44" customHeight="1">
       <c r="A226" s="5" t="n">
@@ -11885,6 +12643,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M226" s="6" t="inlineStr">
+        <is>
+          <t>АО «Благовещенский арматурный завод» — № 10329690 до 16.09.2030</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="44" customHeight="1">
       <c r="A227" s="5" t="n">
@@ -11935,6 +12698,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M227" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="44" customHeight="1">
       <c r="A228" s="5" t="n">
@@ -11985,6 +12753,11 @@
           <t>КИПИКА (прайс 01.10)</t>
         </is>
       </c>
+      <c r="M228" s="6" t="inlineStr">
+        <is>
+          <t>ООО «ЛД Прайд» — № 10826766 до 04.05.2031</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="44" customHeight="1">
       <c r="A229" s="5" t="n">
@@ -12035,6 +12808,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M229" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Бологовский арматурный завод» — № 10895023 до 24.08.2031</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="44" customHeight="1">
       <c r="A230" s="5" t="n">
@@ -12085,6 +12863,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M230" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Бологовский арматурный завод» — № 10895023 до 24.08.2031</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="44" customHeight="1">
       <c r="A231" s="5" t="n">
@@ -12135,6 +12918,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M231" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Бологовский арматурный завод» — № 10895023 до 24.08.2031</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="44" customHeight="1">
       <c r="A232" s="5" t="n">
@@ -12185,6 +12973,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M232" s="6" t="inlineStr">
+        <is>
+          <t>нет: Не найдено: на чугунные (СЧ/КЧ) запорные клапаны 15кч12пМ действующих записей в реестре нет (ОКПД2 28.14.13.110 — только стальные/латунные). Запасной вариант — стальной аналог ПТЗ (15с18п/15с22нж</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="44" customHeight="1">
       <c r="A233" s="5" t="n">
@@ -12235,6 +13028,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M233" s="6" t="inlineStr">
+        <is>
+          <t>нет: Не найдено: на чугунные (СЧ/КЧ) запорные клапаны 15кч16п1 действующих записей в реестре нет (ОКПД2 28.14.13.110 — только стальные/латунные). Запасной вариант — стальной аналог ПТЗ (15с18п/15с22нж</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="44" customHeight="1">
       <c r="A234" s="5" t="n">
@@ -12285,6 +13083,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M234" s="6" t="inlineStr">
+        <is>
+          <t>нет: Не найдено: на чугунные (СЧ/КЧ) запорные клапаны 15кч16п1 действующих записей в реестре нет (ОКПД2 28.14.13.110 — только стальные/латунные). Запасной вариант — стальной аналог ПТЗ (15с18п/15с22нж</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="44" customHeight="1">
       <c r="A235" s="5" t="n">
@@ -12335,6 +13138,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M235" s="6" t="inlineStr">
+        <is>
+          <t>нет: Не найдено: на чугунные (СЧ/КЧ) запорные клапаны 15кч16п1 действующих записей в реестре нет (ОКПД2 28.14.13.110 — только стальные/латунные). Запасной вариант — стальной аналог ПТЗ (15с18п/15с22нж</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="44" customHeight="1">
       <c r="A236" s="5" t="n">
@@ -12385,6 +13193,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M236" s="6" t="inlineStr">
+        <is>
+          <t>нет: Не найдено: на чугунные (СЧ/КЧ) запорные клапаны 15кч19п действующих записей в реестре нет (ОКПД2 28.14.13.110 — только стальные/латунные). Запасной вариант — стальной аналог ПТЗ (15с18п/15с22нж)</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="44" customHeight="1">
       <c r="A237" s="5" t="n">
@@ -12435,6 +13248,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M237" s="6" t="inlineStr">
+        <is>
+          <t>нет: Не найдено: на чугунные (СЧ/КЧ) запорные клапаны 15кч19п действующих записей в реестре нет (ОКПД2 28.14.13.110 — только стальные/латунные). Запасной вариант — стальной аналог ПТЗ (15с18п/15с22нж)</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="44" customHeight="1">
       <c r="A238" s="5" t="n">
@@ -12485,6 +13303,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M238" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="44" customHeight="1">
       <c r="A239" s="5" t="n">
@@ -12535,6 +13358,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M239" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="44" customHeight="1">
       <c r="A240" s="5" t="n">
@@ -12585,6 +13413,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M240" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="44" customHeight="1">
       <c r="A241" s="5" t="n">
@@ -12635,6 +13468,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M241" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="44" customHeight="1">
       <c r="A242" s="5" t="n">
@@ -12685,6 +13523,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M242" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="44" customHeight="1">
       <c r="A243" s="5" t="n">
@@ -12735,6 +13578,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M243" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="44" customHeight="1">
       <c r="A244" s="5" t="n">
@@ -12785,6 +13633,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M244" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="44" customHeight="1">
       <c r="A245" s="5" t="n">
@@ -12835,6 +13688,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M245" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="44" customHeight="1">
       <c r="A246" s="5" t="n">
@@ -12885,6 +13743,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M246" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="44" customHeight="1">
       <c r="A247" s="5" t="n">
@@ -12935,6 +13798,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M247" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="44" customHeight="1">
       <c r="A248" s="5" t="n">
@@ -12985,6 +13853,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M248" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="44" customHeight="1">
       <c r="A249" s="5" t="n">
@@ -13035,6 +13908,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M249" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="44" customHeight="1">
       <c r="A250" s="5" t="n">
@@ -13085,6 +13963,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M250" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="44" customHeight="1">
       <c r="A251" s="5" t="n">
@@ -13135,6 +14018,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M251" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="44" customHeight="1">
       <c r="A252" s="5" t="n">
@@ -13185,6 +14073,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M252" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698937 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="44" customHeight="1">
       <c r="A253" s="5" t="n">
@@ -13235,6 +14128,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M253" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="44" customHeight="1">
       <c r="A254" s="5" t="n">
@@ -13285,6 +14183,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M254" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="44" customHeight="1">
       <c r="A255" s="5" t="n">
@@ -13335,6 +14238,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M255" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="44" customHeight="1">
       <c r="A256" s="5" t="n">
@@ -13385,6 +14293,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M256" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="44" customHeight="1">
       <c r="A257" s="5" t="n">
@@ -13435,6 +14348,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M257" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="44" customHeight="1">
       <c r="A258" s="5" t="n">
@@ -13485,6 +14403,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M258" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="44" customHeight="1">
       <c r="A259" s="5" t="n">
@@ -13535,6 +14458,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M259" s="6" t="inlineStr">
+        <is>
+          <t>ОАО «Литейно-механический завод» — № 10636782 до 15.05.2028</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="44" customHeight="1">
       <c r="A260" s="5" t="n">
@@ -13585,6 +14513,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M260" s="6" t="inlineStr">
+        <is>
+          <t>ОАО «Литейно-механический завод» — № 10636782 до 15.05.2028</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="44" customHeight="1">
       <c r="A261" s="5" t="n">
@@ -13635,6 +14568,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M261" s="6" t="inlineStr">
+        <is>
+          <t>ОАО «Литейно-механический завод» — № 10636782 до 15.05.2028</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="44" customHeight="1">
       <c r="A262" s="5" t="n">
@@ -13685,6 +14623,11 @@
           <t>КИПИКА (прайс 01.10)</t>
         </is>
       </c>
+      <c r="M262" s="6" t="inlineStr">
+        <is>
+          <t>ООО «ЛД Прайд» — № 10826766 до 04.05.2031</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="44" customHeight="1">
       <c r="A263" s="5" t="n">
@@ -13735,6 +14678,7 @@
         </is>
       </c>
       <c r="L263" s="6" t="inlineStr"/>
+      <c r="M263" s="6" t="inlineStr"/>
     </row>
     <row r="264" ht="44" customHeight="1">
       <c r="A264" s="5" t="n">
@@ -13785,6 +14729,7 @@
         </is>
       </c>
       <c r="L264" s="6" t="inlineStr"/>
+      <c r="M264" s="6" t="inlineStr"/>
     </row>
     <row r="265" ht="44" customHeight="1">
       <c r="A265" s="5" t="n">
@@ -13835,6 +14780,7 @@
         </is>
       </c>
       <c r="L265" s="6" t="inlineStr"/>
+      <c r="M265" s="6" t="inlineStr"/>
     </row>
     <row r="266" ht="44" customHeight="1">
       <c r="A266" s="5" t="n">
@@ -13885,6 +14831,7 @@
         </is>
       </c>
       <c r="L266" s="6" t="inlineStr"/>
+      <c r="M266" s="6" t="inlineStr"/>
     </row>
     <row r="267" ht="44" customHeight="1">
       <c r="A267" s="5" t="n">
@@ -13935,6 +14882,7 @@
         </is>
       </c>
       <c r="L267" s="6" t="inlineStr"/>
+      <c r="M267" s="6" t="inlineStr"/>
     </row>
     <row r="268" ht="44" customHeight="1">
       <c r="A268" s="5" t="n">
@@ -13985,6 +14933,7 @@
         </is>
       </c>
       <c r="L268" s="6" t="inlineStr"/>
+      <c r="M268" s="6" t="inlineStr"/>
     </row>
     <row r="269" ht="44" customHeight="1">
       <c r="A269" s="5" t="n">
@@ -14035,6 +14984,7 @@
         </is>
       </c>
       <c r="L269" s="6" t="inlineStr"/>
+      <c r="M269" s="6" t="inlineStr"/>
     </row>
     <row r="270" ht="44" customHeight="1">
       <c r="A270" s="5" t="n">
@@ -14085,6 +15035,7 @@
         </is>
       </c>
       <c r="L270" s="6" t="inlineStr"/>
+      <c r="M270" s="6" t="inlineStr"/>
     </row>
     <row r="271" ht="44" customHeight="1">
       <c r="A271" s="5" t="n">
@@ -14135,6 +15086,7 @@
         </is>
       </c>
       <c r="L271" s="6" t="inlineStr"/>
+      <c r="M271" s="6" t="inlineStr"/>
     </row>
     <row r="272" ht="44" customHeight="1">
       <c r="A272" s="5" t="n">
@@ -14185,6 +15137,7 @@
         </is>
       </c>
       <c r="L272" s="6" t="inlineStr"/>
+      <c r="M272" s="6" t="inlineStr"/>
     </row>
     <row r="273" ht="44" customHeight="1">
       <c r="A273" s="5" t="n">
@@ -14235,6 +15188,7 @@
         </is>
       </c>
       <c r="L273" s="6" t="inlineStr"/>
+      <c r="M273" s="6" t="inlineStr"/>
     </row>
     <row r="274" ht="44" customHeight="1">
       <c r="A274" s="5" t="n">
@@ -14285,6 +15239,7 @@
         </is>
       </c>
       <c r="L274" s="6" t="inlineStr"/>
+      <c r="M274" s="6" t="inlineStr"/>
     </row>
     <row r="275" ht="44" customHeight="1">
       <c r="A275" s="5" t="n">
@@ -14335,6 +15290,7 @@
         </is>
       </c>
       <c r="L275" s="6" t="inlineStr"/>
+      <c r="M275" s="6" t="inlineStr"/>
     </row>
     <row r="276" ht="44" customHeight="1">
       <c r="A276" s="5" t="n">
@@ -14385,6 +15341,7 @@
         </is>
       </c>
       <c r="L276" s="6" t="inlineStr"/>
+      <c r="M276" s="6" t="inlineStr"/>
     </row>
     <row r="277" ht="44" customHeight="1">
       <c r="A277" s="5" t="n">
@@ -14435,6 +15392,7 @@
         </is>
       </c>
       <c r="L277" s="6" t="inlineStr"/>
+      <c r="M277" s="6" t="inlineStr"/>
     </row>
     <row r="278" ht="44" customHeight="1">
       <c r="A278" s="5" t="n">
@@ -14485,6 +15443,7 @@
         </is>
       </c>
       <c r="L278" s="6" t="inlineStr"/>
+      <c r="M278" s="6" t="inlineStr"/>
     </row>
     <row r="279" ht="44" customHeight="1">
       <c r="A279" s="5" t="n">
@@ -14535,6 +15494,7 @@
         </is>
       </c>
       <c r="L279" s="6" t="inlineStr"/>
+      <c r="M279" s="6" t="inlineStr"/>
     </row>
     <row r="280" ht="44" customHeight="1">
       <c r="A280" s="5" t="n">
@@ -14585,6 +15545,7 @@
         </is>
       </c>
       <c r="L280" s="6" t="inlineStr"/>
+      <c r="M280" s="6" t="inlineStr"/>
     </row>
     <row r="281" ht="44" customHeight="1">
       <c r="A281" s="5" t="n">
@@ -14635,6 +15596,7 @@
         </is>
       </c>
       <c r="L281" s="6" t="inlineStr"/>
+      <c r="M281" s="6" t="inlineStr"/>
     </row>
     <row r="282" ht="44" customHeight="1">
       <c r="A282" s="5" t="n">
@@ -14685,6 +15647,7 @@
         </is>
       </c>
       <c r="L282" s="6" t="inlineStr"/>
+      <c r="M282" s="6" t="inlineStr"/>
     </row>
     <row r="283" ht="44" customHeight="1">
       <c r="A283" s="5" t="n">
@@ -14735,6 +15698,7 @@
         </is>
       </c>
       <c r="L283" s="6" t="inlineStr"/>
+      <c r="M283" s="6" t="inlineStr"/>
     </row>
     <row r="284" ht="44" customHeight="1">
       <c r="A284" s="5" t="n">
@@ -14785,6 +15749,7 @@
         </is>
       </c>
       <c r="L284" s="6" t="inlineStr"/>
+      <c r="M284" s="6" t="inlineStr"/>
     </row>
     <row r="285" ht="44" customHeight="1">
       <c r="A285" s="5" t="n">
@@ -14835,6 +15800,7 @@
         </is>
       </c>
       <c r="L285" s="6" t="inlineStr"/>
+      <c r="M285" s="6" t="inlineStr"/>
     </row>
     <row r="286" ht="44" customHeight="1">
       <c r="A286" s="5" t="n">
@@ -14885,6 +15851,7 @@
         </is>
       </c>
       <c r="L286" s="6" t="inlineStr"/>
+      <c r="M286" s="6" t="inlineStr"/>
     </row>
     <row r="287" ht="44" customHeight="1">
       <c r="A287" s="5" t="n">
@@ -14935,6 +15902,7 @@
         </is>
       </c>
       <c r="L287" s="6" t="inlineStr"/>
+      <c r="M287" s="6" t="inlineStr"/>
     </row>
     <row r="288" ht="44" customHeight="1">
       <c r="A288" s="5" t="n">
@@ -14985,6 +15953,7 @@
         </is>
       </c>
       <c r="L288" s="6" t="inlineStr"/>
+      <c r="M288" s="6" t="inlineStr"/>
     </row>
     <row r="289" ht="44" customHeight="1">
       <c r="A289" s="5" t="n">
@@ -15035,6 +16004,7 @@
         </is>
       </c>
       <c r="L289" s="6" t="inlineStr"/>
+      <c r="M289" s="6" t="inlineStr"/>
     </row>
     <row r="290" ht="44" customHeight="1">
       <c r="A290" s="5" t="n">
@@ -15085,6 +16055,7 @@
         </is>
       </c>
       <c r="L290" s="6" t="inlineStr"/>
+      <c r="M290" s="6" t="inlineStr"/>
     </row>
     <row r="291" ht="44" customHeight="1">
       <c r="A291" s="5" t="n">
@@ -15135,6 +16106,7 @@
         </is>
       </c>
       <c r="L291" s="6" t="inlineStr"/>
+      <c r="M291" s="6" t="inlineStr"/>
     </row>
     <row r="292" ht="44" customHeight="1">
       <c r="A292" s="5" t="n">
@@ -15185,6 +16157,7 @@
         </is>
       </c>
       <c r="L292" s="6" t="inlineStr"/>
+      <c r="M292" s="6" t="inlineStr"/>
     </row>
     <row r="293" ht="44" customHeight="1">
       <c r="A293" s="5" t="n">
@@ -15235,6 +16208,7 @@
         </is>
       </c>
       <c r="L293" s="6" t="inlineStr"/>
+      <c r="M293" s="6" t="inlineStr"/>
     </row>
     <row r="294" ht="44" customHeight="1">
       <c r="A294" s="5" t="n">
@@ -15273,6 +16247,7 @@
         </is>
       </c>
       <c r="L294" s="6" t="inlineStr"/>
+      <c r="M294" s="6" t="inlineStr"/>
     </row>
     <row r="295" ht="44" customHeight="1">
       <c r="A295" s="5" t="n">
@@ -15323,6 +16298,7 @@
         </is>
       </c>
       <c r="L295" s="6" t="inlineStr"/>
+      <c r="M295" s="6" t="inlineStr"/>
     </row>
     <row r="296" ht="44" customHeight="1">
       <c r="A296" s="5" t="n">
@@ -15373,6 +16349,7 @@
         </is>
       </c>
       <c r="L296" s="6" t="inlineStr"/>
+      <c r="M296" s="6" t="inlineStr"/>
     </row>
     <row r="297" ht="44" customHeight="1">
       <c r="A297" s="5" t="n">
@@ -15423,6 +16400,7 @@
         </is>
       </c>
       <c r="L297" s="6" t="inlineStr"/>
+      <c r="M297" s="6" t="inlineStr"/>
     </row>
     <row r="298" ht="44" customHeight="1">
       <c r="A298" s="5" t="n">
@@ -15473,6 +16451,7 @@
         </is>
       </c>
       <c r="L298" s="6" t="inlineStr"/>
+      <c r="M298" s="6" t="inlineStr"/>
     </row>
     <row r="299" ht="44" customHeight="1">
       <c r="A299" s="5" t="n">
@@ -15523,6 +16502,7 @@
         </is>
       </c>
       <c r="L299" s="6" t="inlineStr"/>
+      <c r="M299" s="6" t="inlineStr"/>
     </row>
     <row r="300" ht="44" customHeight="1">
       <c r="A300" s="5" t="n">
@@ -15573,6 +16553,7 @@
         </is>
       </c>
       <c r="L300" s="6" t="inlineStr"/>
+      <c r="M300" s="6" t="inlineStr"/>
     </row>
     <row r="301" ht="44" customHeight="1">
       <c r="A301" s="5" t="n">
@@ -15631,6 +16612,7 @@
           <t>ТД АДЛ (Гранвэл)</t>
         </is>
       </c>
+      <c r="M301" s="6" t="inlineStr"/>
     </row>
     <row r="302" ht="44" customHeight="1">
       <c r="A302" s="5" t="n">
@@ -15689,6 +16671,7 @@
           <t>ТД АДЛ (Гранвэл)</t>
         </is>
       </c>
+      <c r="M302" s="6" t="inlineStr"/>
     </row>
     <row r="303" ht="44" customHeight="1">
       <c r="A303" s="5" t="n">
@@ -15747,6 +16730,7 @@
           <t>ТД АДЛ (Гранвэл)</t>
         </is>
       </c>
+      <c r="M303" s="6" t="inlineStr"/>
     </row>
     <row r="304" ht="44" customHeight="1">
       <c r="A304" s="5" t="n">
@@ -15785,6 +16769,7 @@
         </is>
       </c>
       <c r="L304" s="6" t="inlineStr"/>
+      <c r="M304" s="6" t="inlineStr"/>
     </row>
     <row r="305" ht="44" customHeight="1">
       <c r="A305" s="5" t="n">
@@ -15823,6 +16808,7 @@
         </is>
       </c>
       <c r="L305" s="6" t="inlineStr"/>
+      <c r="M305" s="6" t="inlineStr"/>
     </row>
     <row r="306" ht="44" customHeight="1">
       <c r="A306" s="5" t="n">
@@ -15873,6 +16859,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M306" s="6" t="inlineStr">
+        <is>
+          <t>АО «Энерготехномаш» — № 10789125 до 30.06.2031</t>
+        </is>
+      </c>
     </row>
     <row r="307" ht="44" customHeight="1">
       <c r="A307" s="5" t="n">
@@ -15923,6 +16914,7 @@
         </is>
       </c>
       <c r="L307" s="6" t="inlineStr"/>
+      <c r="M307" s="6" t="inlineStr"/>
     </row>
     <row r="308" ht="44" customHeight="1">
       <c r="A308" s="5" t="n">
@@ -15973,6 +16965,7 @@
         </is>
       </c>
       <c r="L308" s="6" t="inlineStr"/>
+      <c r="M308" s="6" t="inlineStr"/>
     </row>
     <row r="309" ht="44" customHeight="1">
       <c r="A309" s="5" t="n">
@@ -16023,6 +17016,7 @@
         </is>
       </c>
       <c r="L309" s="6" t="inlineStr"/>
+      <c r="M309" s="6" t="inlineStr"/>
     </row>
     <row r="310" ht="44" customHeight="1">
       <c r="A310" s="5" t="n">
@@ -16073,6 +17067,11 @@
           <t>ДН.РУ</t>
         </is>
       </c>
+      <c r="M310" s="6" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» — № 10698940 до 17.02.2031</t>
+        </is>
+      </c>
     </row>
     <row r="311" ht="44" customHeight="1">
       <c r="A311" s="5" t="n">
@@ -16123,6 +17122,7 @@
         </is>
       </c>
       <c r="L311" s="6" t="inlineStr"/>
+      <c r="M311" s="6" t="inlineStr"/>
     </row>
     <row r="312" ht="44" customHeight="1">
       <c r="A312" s="5" t="n">
@@ -16173,6 +17173,7 @@
         </is>
       </c>
       <c r="L312" s="6" t="inlineStr"/>
+      <c r="M312" s="6" t="inlineStr"/>
     </row>
     <row r="313" ht="44" customHeight="1">
       <c r="A313" s="5" t="n">
@@ -16223,6 +17224,7 @@
         </is>
       </c>
       <c r="L313" s="6" t="inlineStr"/>
+      <c r="M313" s="6" t="inlineStr"/>
     </row>
     <row r="314" ht="44" customHeight="1">
       <c r="A314" s="5" t="n">
@@ -16273,6 +17275,7 @@
         </is>
       </c>
       <c r="L314" s="6" t="inlineStr"/>
+      <c r="M314" s="6" t="inlineStr"/>
     </row>
     <row r="315" ht="44" customHeight="1">
       <c r="A315" s="5" t="n">
@@ -16323,6 +17326,7 @@
         </is>
       </c>
       <c r="L315" s="6" t="inlineStr"/>
+      <c r="M315" s="6" t="inlineStr"/>
     </row>
     <row r="316" ht="44" customHeight="1">
       <c r="A316" s="5" t="n">
@@ -16373,9 +17377,10 @@
         </is>
       </c>
       <c r="L316" s="6" t="inlineStr"/>
+      <c r="M316" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L316"/>
+  <autoFilter ref="A1:M316"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -16387,7 +17392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -16425,11 +17430,11 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>1.1/1, 1.1/2, 1.1/3, 1.1/4, 1.1/5, 1.1/7, 1.1/8, 1.1/9, 1.1/10, 1.1/11, 1.1/12, 1.1/13, 1.3/1, 1.3/6, 1.3/7, 1.3/8, 1.3/9, 1.3/10, 1.3/11, 1.3/12, 1.3/13, 1.3/14, 1.3/15, 1.3/16, 1.3/17, 1.3/18, 1.3/19, 1.3/20, 1.3/21, 1.3/22, 1.3/25, 1.3/26, 1.3/27, 1.3/28, 1.3/29, 1.3/30, 1.3/31, 1.3/35, 1.3/36, 1.3/37, 1.3/38, 1.3/41, 1.3/42, 1.3/43, 1.3/44, 1.3/48, 1.3/49, 1.3/50, 1.3/51, 1.3/52, 1.3/53, 1.3/54, 1.3/55, 1.3/58, 1.3/59, 1.3/60, 1.3/61, 1.3/62, 1.3/63, 1.3/64, 1.3/65, 1.3/66, 1.3/67, 1.3/68, 1.3/69, 1.3/70, 1.3/71, 1.3/72, 1.3/73, 1.3/74, 1.3/75, 1.3/76, 1.3/77, 1.3/78, 1.3/79, 1.3/80, 1.3/81, 1.3/82, 1.3/83, 1.3/84, 1.3/85, 1.3/86, 1.3/87, 1.3/88, 1.3/89, 1.3/90, 1.3/91, 1.3/92, 1.3/93, 1.3/94, 1.3/95, 1.3/96, 1.3/97, 1.3/98, 1.3/99, 1.5/1, 1.5/2, 1.5/3, 1.6/1, 1.6/2, 1.6/3, 1.6/4, 1.6/5, 1.6/6, 1.6/7, 1.6/8, 1.6/9, 1.6/10, 1.6/11, 1.6/12, 1.6/13, 1.6/14, 1.6/15, 1.6/17, 1.6/18, 1.6/19, 1.6/20, 1.6/21, 1.6/22, 1.6/23, 1.6/24, 1.6/25, 1.6/26, 1.6/27, 1.6/28, 1.6/29, 1.6/30, 1.6/31, 1.6/32, 1.6/33, 1.6/34, 1.6/35, 1.6/36, 1.6/37, 1.6/38, 1.6/39, 1.6/40, 1.6/41, 1.6/42, 1.6/43, 1.6/44, 1.6/45, 1.6/46, 1.6/47, 1.6/48, 1.6/49, 1.7/1, 1.8/1</t>
+          <t>1.1/1, 1.1/2, 1.1/3, 1.1/4, 1.1/5, 1.1/7, 1.1/8, 1.1/9, 1.1/10, 1.1/11, 1.1/12, 1.1/13, 1.3/1, 1.3/6, 1.3/7, 1.3/8, 1.3/10, 1.3/13, 1.3/14, 1.3/15, 1.3/16, 1.3/17, 1.3/18, 1.3/19, 1.3/21, 1.3/25, 1.3/26, 1.3/27, 1.3/28, 1.3/29, 1.3/30, 1.3/31, 1.3/35, 1.3/36, 1.3/37, 1.3/38, 1.3/41, 1.3/42, 1.3/43, 1.3/44, 1.3/48, 1.3/49, 1.3/50, 1.3/51, 1.3/52, 1.3/53, 1.3/54, 1.3/55, 1.3/58, 1.3/59, 1.3/60, 1.3/61, 1.3/62, 1.3/63, 1.3/64, 1.3/65, 1.3/66, 1.3/67, 1.3/68, 1.3/69, 1.3/70, 1.3/71, 1.3/72, 1.3/73, 1.3/74, 1.3/75, 1.3/76, 1.3/77, 1.3/78, 1.3/79, 1.3/80, 1.3/81, 1.3/82, 1.3/83, 1.3/84, 1.3/85, 1.3/86, 1.3/87, 1.3/88, 1.3/89, 1.3/90, 1.3/91, 1.3/92, 1.3/93, 1.3/94, 1.3/95, 1.3/96, 1.3/97, 1.3/98, 1.3/99, 1.5/1, 1.5/2, 1.5/3, 1.6/1, 1.6/2, 1.6/3, 1.6/4, 1.6/5, 1.6/6, 1.6/7, 1.6/8, 1.6/9, 1.6/10, 1.6/11, 1.6/12, 1.6/13, 1.6/14, 1.6/15, 1.6/17, 1.6/18, 1.6/19, 1.6/20, 1.6/21, 1.6/22, 1.6/23, 1.6/24, 1.6/25, 1.6/26, 1.6/27, 1.6/28, 1.6/29, 1.6/30, 1.6/31, 1.6/32, 1.6/33, 1.6/34, 1.6/35, 1.6/36, 1.6/37, 1.6/38, 1.6/39, 1.6/40, 1.6/41, 1.6/42, 1.6/43, 1.6/44, 1.6/45, 1.6/46, 1.6/47, 1.6/48, 1.6/49, 1.7/1, 1.8/1</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
@@ -16453,26 +17458,6 @@
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Добрый день! Для заявки в ПАО «Камчатскэнерго» (32616346943, нацрежим ПП 1875 — ограничение) просим по каждой позиции вашего счёта/КП указать: завод-изготовитель, страну происхождения, номер реестровой записи из реестра российской промышленной продукции (ПП 719) или евразийского реестра, срок действия записи, и приложить выписку из ГИСП. Позиции иностранного производства без записи в реестре — прошу заменить на российские аналоги.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Лидер-Энерго</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>1.3/151, 1.3/152, 1.3/153</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Добрый день! Для заявки в ПАО «Камчатскэнерго» (32616346943, нацрежим ПП 1875 — ограничение) просим по каждой позиции вашего счёта/КП указать: завод-изготовитель, страну происхождения, номер реестровой записи из реестра российской промышленной продукции (ПП 719) или евразийского реестра, срок действия записи, и приложить выписку из ГИСП. Позиции иностранного производства без записи в реестре — прошу заменить на российские аналоги.</t>
         </is>
